--- a/docs/design/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>ダウンロード・プレビューのテストケースを削除（ファイルダウンロード画面 SCR-022 へ移行）。本画面は一覧／アップロード／削除専用。</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ70"/>
+  <dimension ref="A1:BQ69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8174,7 +8234,7 @@
       <c r="BP17" s="10" t="n"/>
       <c r="BQ17" s="11" t="n"/>
     </row>
-    <row r="18" ht="272" customHeight="1">
+    <row r="18" ht="304" customHeight="1">
       <c r="A18" s="44" t="n">
         <v>6</v>
       </c>
@@ -8187,7 +8247,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="46" t="inlineStr">
         <is>
-          <t>DataScope違反: JA_HONTEN が他JAのファイルをダウンロード</t>
+          <t>URL直接攻撃: JA_HONTEN が他JAのIDを指定してアップロード</t>
         </is>
       </c>
       <c r="F18" s="10" t="n"/>
@@ -8197,8 +8257,7 @@
       <c r="J18" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id = 12345）
-・ログイン済 + MFA認証済
-・他JA（ja_id = 67890）のファイル（`file_upload_id = 202`）が存在</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K18" s="10" t="n"/>
@@ -8223,7 +8282,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DevToolsで GET `/api/v1/file-upload/202/download` を直接送信（自JAスコープ外のファイル）
+            <t xml:space="preserve">DevToolsで POST `/api/v1/file-upload` を multipart/form-data で送信。`ja_ids[]=67890`（自JAスコープ外）＋有効なファイル1件を指定
 </t>
           </r>
           <r>
@@ -8240,7 +8299,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT * FROM t_log WHERE result_status = 2 AND target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE ja_id = 67890 AND deleted_at IS NULL`（送信前後で件数比較）</t>
           </r>
         </is>
       </c>
@@ -8283,15 +8342,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・エラーログが1件以上記録されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・ファイルのバイナリがレスポンスされないこと
+            <t xml:space="preserve">・`t_file_upload` に他JA（ja_id=67890）向けの新規レコードが登録されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・物理ファイルがストレージに保存されないこと
 </t>
           </r>
           <r>
@@ -8308,7 +8367,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・スコープ外データへのアクセスがBE APIガードで遮断されること</t>
+            <t>・リクエストボディの ja_ids はサーバー側のDataScopeで検証され、スコープ外IDは拒否されること</t>
           </r>
         </is>
       </c>
@@ -8356,7 +8415,8 @@
       <c r="BJ18" s="11" t="n"/>
       <c r="BK18" s="46" t="inlineStr">
         <is>
-          <t>クリティカル — 失敗時は他JAデータ漏洩を意味し、セキュリティインシデントとして扱う。</t>
+          <t>クリティカル — 失敗時は他JAへの不正書き込みを意味する。
+---</t>
         </is>
       </c>
       <c r="BL18" s="10" t="n"/>
@@ -8366,191 +8426,74 @@
       <c r="BP18" s="10" t="n"/>
       <c r="BQ18" s="11" t="n"/>
     </row>
-    <row r="19" ht="304" customHeight="1">
-      <c r="A19" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-007</t>
-        </is>
-      </c>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>画面表示・レスポンシブ（Layout &amp; Responsive）</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="46" t="inlineStr">
-        <is>
-          <t>URL直接攻撃: JA_HONTEN が他JAのIDを指定してアップロード</t>
-        </is>
-      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id = 12345）
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DevToolsで POST `/api/v1/file-upload` を multipart/form-data で送信。`ja_ids[]=67890`（自JAスコープ外）＋有効なファイル1件を指定
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE ja_id = 67890 AND deleted_at IS NULL`（送信前後で件数比較）</t>
-          </r>
-        </is>
-      </c>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
       <c r="R19" s="10" t="n"/>
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">HTTPステータスコード403が返却されること（`error_code: DATA_SCOPE_VIOLATION`、メッセージ `このデータへのアクセス権限がありません。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・`t_file_upload` に他JA（ja_id=67890）向けの新規レコードが登録されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・物理ファイルがストレージに保存されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・リクエストボディの ja_ids はサーバー側のDataScopeで検証され、スコープ外IDは拒否されること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
       <c r="Y19" s="10" t="n"/>
       <c r="Z19" s="10" t="n"/>
       <c r="AA19" s="10" t="n"/>
       <c r="AB19" s="10" t="n"/>
       <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="11" t="n"/>
-      <c r="AE19" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF19" s="11" t="n"/>
-      <c r="AG19" s="45" t="inlineStr"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
       <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="11" t="n"/>
-      <c r="AJ19" s="45" t="inlineStr"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
       <c r="AK19" s="10" t="n"/>
-      <c r="AL19" s="11" t="n"/>
-      <c r="AM19" s="45" t="inlineStr"/>
+      <c r="AL19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n"/>
       <c r="AN19" s="10" t="n"/>
-      <c r="AO19" s="11" t="n"/>
-      <c r="AP19" s="45" t="inlineStr"/>
+      <c r="AO19" s="10" t="n"/>
+      <c r="AP19" s="10" t="n"/>
       <c r="AQ19" s="10" t="n"/>
-      <c r="AR19" s="11" t="n"/>
-      <c r="AS19" s="45" t="inlineStr"/>
+      <c r="AR19" s="10" t="n"/>
+      <c r="AS19" s="10" t="n"/>
       <c r="AT19" s="10" t="n"/>
-      <c r="AU19" s="11" t="n"/>
-      <c r="AV19" s="45" t="inlineStr"/>
+      <c r="AU19" s="10" t="n"/>
+      <c r="AV19" s="10" t="n"/>
       <c r="AW19" s="10" t="n"/>
-      <c r="AX19" s="11" t="n"/>
-      <c r="AY19" s="45" t="inlineStr"/>
+      <c r="AX19" s="10" t="n"/>
+      <c r="AY19" s="10" t="n"/>
       <c r="AZ19" s="10" t="n"/>
-      <c r="BA19" s="11" t="n"/>
-      <c r="BB19" s="45" t="inlineStr"/>
+      <c r="BA19" s="10" t="n"/>
+      <c r="BB19" s="10" t="n"/>
       <c r="BC19" s="10" t="n"/>
-      <c r="BD19" s="11" t="n"/>
-      <c r="BE19" s="45" t="inlineStr"/>
+      <c r="BD19" s="10" t="n"/>
+      <c r="BE19" s="10" t="n"/>
       <c r="BF19" s="10" t="n"/>
-      <c r="BG19" s="11" t="n"/>
-      <c r="BH19" s="45" t="inlineStr"/>
+      <c r="BG19" s="10" t="n"/>
+      <c r="BH19" s="10" t="n"/>
       <c r="BI19" s="10" t="n"/>
-      <c r="BJ19" s="11" t="n"/>
-      <c r="BK19" s="46" t="inlineStr">
-        <is>
-          <t>クリティカル — 失敗時は他JAへの不正書き込みを意味する。
----</t>
-        </is>
-      </c>
+      <c r="BJ19" s="10" t="n"/>
+      <c r="BK19" s="10" t="n"/>
       <c r="BL19" s="10" t="n"/>
       <c r="BM19" s="10" t="n"/>
       <c r="BN19" s="10" t="n"/>
@@ -8558,74 +8501,143 @@
       <c r="BP19" s="10" t="n"/>
       <c r="BQ19" s="11" t="n"/>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>画面表示・レスポンシブ（Layout &amp; Responsive）</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n"/>
+    <row r="20" ht="112" customHeight="1">
+      <c r="A20" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-007</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>画面初期表示（全項目空白）</t>
+        </is>
+      </c>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済</t>
+        </is>
+      </c>
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>URL `/file-upload` へ遷移し、画面を表示</t>
+          </r>
+        </is>
+      </c>
       <c r="R20" s="10" t="n"/>
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
       <c r="V20" s="10" t="n"/>
-      <c r="W20" s="10" t="n"/>
-      <c r="X20" s="10" t="n"/>
+      <c r="W20" s="11" t="n"/>
+      <c r="X20" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・画面が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・対象JA、ファイル選択、削除予定日の各入力項目が初期状態（空白／未選択）で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・画面崩れが発生しないこと</t>
+          </r>
+        </is>
+      </c>
       <c r="Y20" s="10" t="n"/>
       <c r="Z20" s="10" t="n"/>
       <c r="AA20" s="10" t="n"/>
       <c r="AB20" s="10" t="n"/>
       <c r="AC20" s="10" t="n"/>
-      <c r="AD20" s="10" t="n"/>
-      <c r="AE20" s="10" t="n"/>
-      <c r="AF20" s="10" t="n"/>
-      <c r="AG20" s="10" t="n"/>
+      <c r="AD20" s="11" t="n"/>
+      <c r="AE20" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF20" s="11" t="n"/>
+      <c r="AG20" s="45" t="inlineStr"/>
       <c r="AH20" s="10" t="n"/>
-      <c r="AI20" s="10" t="n"/>
-      <c r="AJ20" s="10" t="n"/>
+      <c r="AI20" s="11" t="n"/>
+      <c r="AJ20" s="45" t="inlineStr"/>
       <c r="AK20" s="10" t="n"/>
-      <c r="AL20" s="10" t="n"/>
-      <c r="AM20" s="10" t="n"/>
+      <c r="AL20" s="11" t="n"/>
+      <c r="AM20" s="45" t="inlineStr"/>
       <c r="AN20" s="10" t="n"/>
-      <c r="AO20" s="10" t="n"/>
-      <c r="AP20" s="10" t="n"/>
+      <c r="AO20" s="11" t="n"/>
+      <c r="AP20" s="45" t="inlineStr"/>
       <c r="AQ20" s="10" t="n"/>
-      <c r="AR20" s="10" t="n"/>
-      <c r="AS20" s="10" t="n"/>
+      <c r="AR20" s="11" t="n"/>
+      <c r="AS20" s="45" t="inlineStr"/>
       <c r="AT20" s="10" t="n"/>
-      <c r="AU20" s="10" t="n"/>
-      <c r="AV20" s="10" t="n"/>
+      <c r="AU20" s="11" t="n"/>
+      <c r="AV20" s="45" t="inlineStr"/>
       <c r="AW20" s="10" t="n"/>
-      <c r="AX20" s="10" t="n"/>
-      <c r="AY20" s="10" t="n"/>
+      <c r="AX20" s="11" t="n"/>
+      <c r="AY20" s="45" t="inlineStr"/>
       <c r="AZ20" s="10" t="n"/>
-      <c r="BA20" s="10" t="n"/>
-      <c r="BB20" s="10" t="n"/>
+      <c r="BA20" s="11" t="n"/>
+      <c r="BB20" s="45" t="inlineStr"/>
       <c r="BC20" s="10" t="n"/>
-      <c r="BD20" s="10" t="n"/>
-      <c r="BE20" s="10" t="n"/>
+      <c r="BD20" s="11" t="n"/>
+      <c r="BE20" s="45" t="inlineStr"/>
       <c r="BF20" s="10" t="n"/>
-      <c r="BG20" s="10" t="n"/>
-      <c r="BH20" s="10" t="n"/>
+      <c r="BG20" s="11" t="n"/>
+      <c r="BH20" s="45" t="inlineStr"/>
       <c r="BI20" s="10" t="n"/>
-      <c r="BJ20" s="10" t="n"/>
-      <c r="BK20" s="10" t="n"/>
+      <c r="BJ20" s="11" t="n"/>
+      <c r="BK20" s="46" t="inlineStr"/>
       <c r="BL20" s="10" t="n"/>
       <c r="BM20" s="10" t="n"/>
       <c r="BN20" s="10" t="n"/>
@@ -8633,7 +8645,7 @@
       <c r="BP20" s="10" t="n"/>
       <c r="BQ20" s="11" t="n"/>
     </row>
-    <row r="21" ht="112" customHeight="1">
+    <row r="21" ht="224" customHeight="1">
       <c r="A21" s="44" t="n">
         <v>8</v>
       </c>
@@ -8646,7 +8658,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>画面初期表示（全項目空白）</t>
+          <t>対象JA選択エリアの表示</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -8681,7 +8693,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>URL `/file-upload` へ遷移し、画面を表示</t>
+            <t xml:space="preserve">画面の「対象JA選択」エリアを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>「都道府県コード」セレクトボックスを押下し、続いて「対象JA」セレクトボックスを確認</t>
           </r>
         </is>
       </c>
@@ -8707,23 +8736,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・画面が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・対象JA、ファイル選択、削除予定日の各入力項目が初期状態（空白／未選択）で表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・画面崩れが発生しないこと</t>
+            <t xml:space="preserve">・「都道府県コード」「都道府県名」「対象JA」のセレクトボックス、「追加」ボタン、「削除」ボタンが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「都道府県名」は読み取り専用で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「対象JA」セレクトボックスにJAコード＋JA名の一覧が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「対象JA」セレクトボックスで検索ができること</t>
           </r>
         </is>
       </c>
@@ -8777,7 +8823,7 @@
       <c r="BP21" s="10" t="n"/>
       <c r="BQ21" s="11" t="n"/>
     </row>
-    <row r="22" ht="224" customHeight="1">
+    <row r="22" ht="176" customHeight="1">
       <c r="A22" s="44" t="n">
         <v>9</v>
       </c>
@@ -8790,7 +8836,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="46" t="inlineStr">
         <is>
-          <t>対象JA選択エリアの表示</t>
+          <t>ファイル選択エリアの表示</t>
         </is>
       </c>
       <c r="F22" s="10" t="n"/>
@@ -8825,7 +8871,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面の「対象JA選択」エリアを確認
+            <t xml:space="preserve">画面の「ファイル選択」エリアを確認
 </t>
           </r>
           <r>
@@ -8842,7 +8888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>「都道府県コード」セレクトボックスを押下し、続いて「対象JA」セレクトボックスを確認</t>
+            <t>ファイルを1件選択した後、「削除予定日」項目を確認</t>
           </r>
         </is>
       </c>
@@ -8868,15 +8914,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「都道府県コード」「都道府県名」「対象JA」のセレクトボックス、「追加」ボタン、「削除」ボタンが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「都道府県名」は読み取り専用で表示されること
+            <t xml:space="preserve">・ドラッグアンドドロップ対応のファイル選択エリアと「参照」ボタンが表示されること
 </t>
           </r>
           <r>
@@ -8893,15 +8931,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「対象JA」セレクトボックスにJAコード＋JA名の一覧が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・「対象JA」セレクトボックスで検索ができること</t>
+            <t xml:space="preserve">・「削除予定日」がカレンダー入力項目として表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・選択したファイルが「ファイル名＋サイズ」の形式で一覧に表示されること</t>
           </r>
         </is>
       </c>
@@ -8955,7 +8993,7 @@
       <c r="BP22" s="10" t="n"/>
       <c r="BQ22" s="11" t="n"/>
     </row>
-    <row r="23" ht="176" customHeight="1">
+    <row r="23" ht="64" customHeight="1">
       <c r="A23" s="44" t="n">
         <v>10</v>
       </c>
@@ -8968,7 +9006,7 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>ファイル選択エリアの表示</t>
+          <t>アクションボタンの表示</t>
         </is>
       </c>
       <c r="F23" s="10" t="n"/>
@@ -9003,24 +9041,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面の「ファイル選択」エリアを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>ファイルを1件選択した後、「削除予定日」項目を確認</t>
+            <t>画面下部のアクションボタンエリアを確認</t>
           </r>
         </is>
       </c>
@@ -9046,32 +9067,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ドラッグアンドドロップ対応のファイル選択エリアと「参照」ボタンが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「削除予定日」がカレンダー入力項目として表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・選択したファイルが「ファイル名＋サイズ」の形式で一覧に表示されること</t>
+            <t>・「アップロード実行」ボタンと「クリア」ボタンが表示されること</t>
           </r>
         </is>
       </c>
@@ -9125,7 +9121,7 @@
       <c r="BP23" s="10" t="n"/>
       <c r="BQ23" s="11" t="n"/>
     </row>
-    <row r="24" ht="64" customHeight="1">
+    <row r="24" ht="336" customHeight="1">
       <c r="A24" s="44" t="n">
         <v>11</v>
       </c>
@@ -9138,7 +9134,7 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="46" t="inlineStr">
         <is>
-          <t>アクションボタンの表示</t>
+          <t>アップロード済みファイル一覧テーブルの表示</t>
         </is>
       </c>
       <c r="F24" s="10" t="n"/>
@@ -9148,7 +9144,8 @@
       <c r="J24" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
+・ログイン済 + MFA認証済
+・アップロード済みファイルが複数件存在（`deleted_at` が NULL の行と NOT NULL の行を各1件以上）</t>
         </is>
       </c>
       <c r="K24" s="10" t="n"/>
@@ -9173,7 +9170,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>画面下部のアクションボタンエリアを確認</t>
+            <t xml:space="preserve">画面下部の「アップロードされたファイルリスト」テーブルを確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>各行の「通知ステータス」列と「削除」ボタンの状態を確認</t>
           </r>
         </is>
       </c>
@@ -9199,7 +9213,48 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・「アップロード実行」ボタンと「クリア」ボタンが表示されること</t>
+            <t xml:space="preserve">・「ファイル名」「サイズ」「通知ステータス」「削除予定日」「削除日」「操作（削除ボタン）」の各列が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「削除日」列は `deleted_at` が NULL の場合「-」、NOT NULL の場合 yyyymmdd 形式で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「通知ステータス」列に「未送信」「送信中」「完了」「一部失敗」のいずれかのバッジが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`deleted_at` が NULL の行は「削除」ボタンが活性状態で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`deleted_at` が NOT NULL の行は「削除」ボタンが非活性状態で表示されること</t>
           </r>
         </is>
       </c>
@@ -9253,7 +9308,7 @@
       <c r="BP24" s="10" t="n"/>
       <c r="BQ24" s="11" t="n"/>
     </row>
-    <row r="25" ht="336" customHeight="1">
+    <row r="25" ht="80" customHeight="1">
       <c r="A25" s="44" t="n">
         <v>12</v>
       </c>
@@ -9266,7 +9321,7 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="46" t="inlineStr">
         <is>
-          <t>アップロード済みファイル一覧テーブルの表示</t>
+          <t>レスポンシブ表示（画面崩れなし）</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -9276,8 +9331,7 @@
       <c r="J25" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・アップロード済みファイルが複数件存在（`deleted_at` が NULL の行と NOT NULL の行を各1件以上）</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K25" s="10" t="n"/>
@@ -9302,24 +9356,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">画面下部の「アップロードされたファイルリスト」テーブルを確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>各行の「通知ステータス」列と「削除」ボタンの状態を確認</t>
+            <t>ブラウザ幅を 1280px / 768px / 375px の各ブレークポイントに変更し、画面を確認</t>
           </r>
         </is>
       </c>
@@ -9345,48 +9382,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「ファイル名」「サイズ」「通知ステータス」「削除予定日」「削除日」「操作（削除ボタン）」の各列が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「削除日」列は `deleted_at` が NULL の場合「-」、NOT NULL の場合 yyyymmdd 形式で表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「通知ステータス」列に「未送信」「送信中」「完了」「一部失敗」のいずれかのバッジが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・`deleted_at` が NULL の行は「削除」ボタンが活性状態で表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`deleted_at` が NOT NULL の行は「削除」ボタンが非活性状態で表示されること</t>
+            <t xml:space="preserve">・各ブレークポイントで画面崩れが発生しないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・横スクロールが意図しない形で発生しないこと</t>
           </r>
         </is>
       </c>
@@ -9440,7 +9444,7 @@
       <c r="BP25" s="10" t="n"/>
       <c r="BQ25" s="11" t="n"/>
     </row>
-    <row r="26" ht="80" customHeight="1">
+    <row r="26" ht="144" customHeight="1">
       <c r="A26" s="44" t="n">
         <v>13</v>
       </c>
@@ -9453,7 +9457,7 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="46" t="inlineStr">
         <is>
-          <t>レスポンシブ表示（画面崩れなし）</t>
+          <t>キーボード操作（Tab順）</t>
         </is>
       </c>
       <c r="F26" s="10" t="n"/>
@@ -9488,7 +9492,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>ブラウザ幅を 1280px / 768px / 375px の各ブレークポイントに変更し、画面を確認</t>
+            <t xml:space="preserve">Tab キーで各入力項目・ボタンを順に移動
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>ボタンに Enter キーでフォーカスし操作を確認</t>
           </r>
         </is>
       </c>
@@ -9514,15 +9535,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・各ブレークポイントで画面崩れが発生しないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・横スクロールが意図しない形で発生しないこと</t>
+            <t xml:space="preserve">・Tab 順が画面の表示順（対象JA → ファイル選択 → 削除予定日 → アクションボタン）に沿っていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・フォーカスされたボタンが Enter キーで操作できること</t>
           </r>
         </is>
       </c>
@@ -9568,7 +9598,12 @@
       <c r="BH26" s="45" t="inlineStr"/>
       <c r="BI26" s="10" t="n"/>
       <c r="BJ26" s="11" t="n"/>
-      <c r="BK26" s="46" t="inlineStr"/>
+      <c r="BK26" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL26" s="10" t="n"/>
       <c r="BM26" s="10" t="n"/>
       <c r="BN26" s="10" t="n"/>
@@ -9576,166 +9611,74 @@
       <c r="BP26" s="10" t="n"/>
       <c r="BQ26" s="11" t="n"/>
     </row>
-    <row r="27" ht="144" customHeight="1">
-      <c r="A27" s="44" t="n">
-        <v>14</v>
-      </c>
-      <c r="B27" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-014</t>
-        </is>
-      </c>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>ヘッダー・パンくず（Header &amp; Breadcrumb）</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="46" t="inlineStr">
-        <is>
-          <t>キーボード操作（Tab順）</t>
-        </is>
-      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Tab キーで各入力項目・ボタンを順に移動
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>ボタンに Enter キーでフォーカスし操作を確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Tab 順が画面の表示順（対象JA → ファイル選択 → 削除予定日 → アクションボタン）に沿っていること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・フォーカスされたボタンが Enter キーで操作できること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="10" t="n"/>
       <c r="AC27" s="10" t="n"/>
-      <c r="AD27" s="11" t="n"/>
-      <c r="AE27" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF27" s="11" t="n"/>
-      <c r="AG27" s="45" t="inlineStr"/>
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="10" t="n"/>
+      <c r="AF27" s="10" t="n"/>
+      <c r="AG27" s="10" t="n"/>
       <c r="AH27" s="10" t="n"/>
-      <c r="AI27" s="11" t="n"/>
-      <c r="AJ27" s="45" t="inlineStr"/>
+      <c r="AI27" s="10" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="10" t="n"/>
-      <c r="AL27" s="11" t="n"/>
-      <c r="AM27" s="45" t="inlineStr"/>
+      <c r="AL27" s="10" t="n"/>
+      <c r="AM27" s="10" t="n"/>
       <c r="AN27" s="10" t="n"/>
-      <c r="AO27" s="11" t="n"/>
-      <c r="AP27" s="45" t="inlineStr"/>
+      <c r="AO27" s="10" t="n"/>
+      <c r="AP27" s="10" t="n"/>
       <c r="AQ27" s="10" t="n"/>
-      <c r="AR27" s="11" t="n"/>
-      <c r="AS27" s="45" t="inlineStr"/>
+      <c r="AR27" s="10" t="n"/>
+      <c r="AS27" s="10" t="n"/>
       <c r="AT27" s="10" t="n"/>
-      <c r="AU27" s="11" t="n"/>
-      <c r="AV27" s="45" t="inlineStr"/>
+      <c r="AU27" s="10" t="n"/>
+      <c r="AV27" s="10" t="n"/>
       <c r="AW27" s="10" t="n"/>
-      <c r="AX27" s="11" t="n"/>
-      <c r="AY27" s="45" t="inlineStr"/>
+      <c r="AX27" s="10" t="n"/>
+      <c r="AY27" s="10" t="n"/>
       <c r="AZ27" s="10" t="n"/>
-      <c r="BA27" s="11" t="n"/>
-      <c r="BB27" s="45" t="inlineStr"/>
+      <c r="BA27" s="10" t="n"/>
+      <c r="BB27" s="10" t="n"/>
       <c r="BC27" s="10" t="n"/>
-      <c r="BD27" s="11" t="n"/>
-      <c r="BE27" s="45" t="inlineStr"/>
+      <c r="BD27" s="10" t="n"/>
+      <c r="BE27" s="10" t="n"/>
       <c r="BF27" s="10" t="n"/>
-      <c r="BG27" s="11" t="n"/>
-      <c r="BH27" s="45" t="inlineStr"/>
+      <c r="BG27" s="10" t="n"/>
+      <c r="BH27" s="10" t="n"/>
       <c r="BI27" s="10" t="n"/>
-      <c r="BJ27" s="11" t="n"/>
-      <c r="BK27" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ27" s="10" t="n"/>
+      <c r="BK27" s="10" t="n"/>
       <c r="BL27" s="10" t="n"/>
       <c r="BM27" s="10" t="n"/>
       <c r="BN27" s="10" t="n"/>
@@ -9743,74 +9686,127 @@
       <c r="BP27" s="10" t="n"/>
       <c r="BQ27" s="11" t="n"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>ヘッダー・パンくず（Header &amp; Breadcrumb）</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n"/>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-014</t>
+        </is>
+      </c>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>パンくずリストの表示</t>
+        </is>
+      </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済</t>
+        </is>
+      </c>
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="n"/>
       <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="10" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>URL `/file-upload` へ遷移し、画面上部のパンくずリストを確認</t>
+          </r>
+        </is>
+      </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="10" t="n"/>
+      <c r="W28" s="11" t="n"/>
+      <c r="X28" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・パンくずリストに「ホーム ＞ ファイルアップロード」が表示されること</t>
+          </r>
+        </is>
+      </c>
       <c r="Y28" s="10" t="n"/>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="10" t="n"/>
       <c r="AC28" s="10" t="n"/>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="10" t="n"/>
-      <c r="AF28" s="10" t="n"/>
-      <c r="AG28" s="10" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+      <c r="AE28" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF28" s="11" t="n"/>
+      <c r="AG28" s="45" t="inlineStr"/>
       <c r="AH28" s="10" t="n"/>
-      <c r="AI28" s="10" t="n"/>
-      <c r="AJ28" s="10" t="n"/>
+      <c r="AI28" s="11" t="n"/>
+      <c r="AJ28" s="45" t="inlineStr"/>
       <c r="AK28" s="10" t="n"/>
-      <c r="AL28" s="10" t="n"/>
-      <c r="AM28" s="10" t="n"/>
+      <c r="AL28" s="11" t="n"/>
+      <c r="AM28" s="45" t="inlineStr"/>
       <c r="AN28" s="10" t="n"/>
-      <c r="AO28" s="10" t="n"/>
-      <c r="AP28" s="10" t="n"/>
+      <c r="AO28" s="11" t="n"/>
+      <c r="AP28" s="45" t="inlineStr"/>
       <c r="AQ28" s="10" t="n"/>
-      <c r="AR28" s="10" t="n"/>
-      <c r="AS28" s="10" t="n"/>
+      <c r="AR28" s="11" t="n"/>
+      <c r="AS28" s="45" t="inlineStr"/>
       <c r="AT28" s="10" t="n"/>
-      <c r="AU28" s="10" t="n"/>
-      <c r="AV28" s="10" t="n"/>
+      <c r="AU28" s="11" t="n"/>
+      <c r="AV28" s="45" t="inlineStr"/>
       <c r="AW28" s="10" t="n"/>
-      <c r="AX28" s="10" t="n"/>
-      <c r="AY28" s="10" t="n"/>
+      <c r="AX28" s="11" t="n"/>
+      <c r="AY28" s="45" t="inlineStr"/>
       <c r="AZ28" s="10" t="n"/>
-      <c r="BA28" s="10" t="n"/>
-      <c r="BB28" s="10" t="n"/>
+      <c r="BA28" s="11" t="n"/>
+      <c r="BB28" s="45" t="inlineStr"/>
       <c r="BC28" s="10" t="n"/>
-      <c r="BD28" s="10" t="n"/>
-      <c r="BE28" s="10" t="n"/>
+      <c r="BD28" s="11" t="n"/>
+      <c r="BE28" s="45" t="inlineStr"/>
       <c r="BF28" s="10" t="n"/>
-      <c r="BG28" s="10" t="n"/>
-      <c r="BH28" s="10" t="n"/>
+      <c r="BG28" s="11" t="n"/>
+      <c r="BH28" s="45" t="inlineStr"/>
       <c r="BI28" s="10" t="n"/>
-      <c r="BJ28" s="10" t="n"/>
-      <c r="BK28" s="10" t="n"/>
+      <c r="BJ28" s="11" t="n"/>
+      <c r="BK28" s="46" t="inlineStr"/>
       <c r="BL28" s="10" t="n"/>
       <c r="BM28" s="10" t="n"/>
       <c r="BN28" s="10" t="n"/>
@@ -9818,7 +9814,7 @@
       <c r="BP28" s="10" t="n"/>
       <c r="BQ28" s="11" t="n"/>
     </row>
-    <row r="29" ht="64" customHeight="1">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="44" t="n">
         <v>15</v>
       </c>
@@ -9831,7 +9827,7 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="46" t="inlineStr">
         <is>
-          <t>パンくずリストの表示</t>
+          <t>パンくず「ホーム」クリックでダッシュボードへ遷移</t>
         </is>
       </c>
       <c r="F29" s="10" t="n"/>
@@ -9866,7 +9862,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>URL `/file-upload` へ遷移し、画面上部のパンくずリストを確認</t>
+            <t>パンくずリストの「ホーム」を押下</t>
           </r>
         </is>
       </c>
@@ -9892,7 +9888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・パンくずリストに「ホーム ＞ ファイルアップロード」が表示されること</t>
+            <t>・`/dashboard` へ遷移すること</t>
           </r>
         </is>
       </c>
@@ -9946,7 +9942,7 @@
       <c r="BP29" s="10" t="n"/>
       <c r="BQ29" s="11" t="n"/>
     </row>
-    <row r="30" ht="48" customHeight="1">
+    <row r="30" ht="64" customHeight="1">
       <c r="A30" s="44" t="n">
         <v>16</v>
       </c>
@@ -9959,7 +9955,7 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="46" t="inlineStr">
         <is>
-          <t>パンくず「ホーム」クリックでダッシュボードへ遷移</t>
+          <t>ページタイトルの表示</t>
         </is>
       </c>
       <c r="F30" s="10" t="n"/>
@@ -9994,7 +9990,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>パンくずリストの「ホーム」を押下</t>
+            <t>URL `/file-upload` へ遷移し、ページタイトルを確認</t>
           </r>
         </is>
       </c>
@@ -10020,7 +10016,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`/dashboard` へ遷移すること</t>
+            <t>・ページタイトルに「ファイルアップロード画面」が表示されること</t>
           </r>
         </is>
       </c>
@@ -10074,7 +10070,7 @@
       <c r="BP30" s="10" t="n"/>
       <c r="BQ30" s="11" t="n"/>
     </row>
-    <row r="31" ht="64" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="44" t="n">
         <v>17</v>
       </c>
@@ -10087,7 +10083,7 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>ページタイトルの表示</t>
+          <t>ヘッダーにログインユーザー名が表示される</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -10122,7 +10118,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>URL `/file-upload` へ遷移し、ページタイトルを確認</t>
+            <t>画面上部のヘッダーを確認</t>
           </r>
         </is>
       </c>
@@ -10148,7 +10144,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・ページタイトルに「ファイルアップロード画面」が表示されること</t>
+            <t>・ログインユーザー名が表示されること</t>
           </r>
         </is>
       </c>
@@ -10194,7 +10190,12 @@
       <c r="BH31" s="45" t="inlineStr"/>
       <c r="BI31" s="10" t="n"/>
       <c r="BJ31" s="11" t="n"/>
-      <c r="BK31" s="46" t="inlineStr"/>
+      <c r="BK31" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL31" s="10" t="n"/>
       <c r="BM31" s="10" t="n"/>
       <c r="BN31" s="10" t="n"/>
@@ -10202,132 +10203,74 @@
       <c r="BP31" s="10" t="n"/>
       <c r="BQ31" s="11" t="n"/>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="44" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-018</t>
-        </is>
-      </c>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>入力バリデーション（Input Validation）</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="46" t="inlineStr">
-        <is>
-          <t>ヘッダーにログインユーザー名が表示される</t>
-        </is>
-      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="10" t="n"/>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>画面上部のヘッダーを確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・ログインユーザー名が表示されること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="10" t="n"/>
       <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="11" t="n"/>
-      <c r="AE32" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF32" s="11" t="n"/>
-      <c r="AG32" s="45" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
       <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="11" t="n"/>
-      <c r="AJ32" s="45" t="inlineStr"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="10" t="n"/>
-      <c r="AL32" s="11" t="n"/>
-      <c r="AM32" s="45" t="inlineStr"/>
+      <c r="AL32" s="10" t="n"/>
+      <c r="AM32" s="10" t="n"/>
       <c r="AN32" s="10" t="n"/>
-      <c r="AO32" s="11" t="n"/>
-      <c r="AP32" s="45" t="inlineStr"/>
+      <c r="AO32" s="10" t="n"/>
+      <c r="AP32" s="10" t="n"/>
       <c r="AQ32" s="10" t="n"/>
-      <c r="AR32" s="11" t="n"/>
-      <c r="AS32" s="45" t="inlineStr"/>
+      <c r="AR32" s="10" t="n"/>
+      <c r="AS32" s="10" t="n"/>
       <c r="AT32" s="10" t="n"/>
-      <c r="AU32" s="11" t="n"/>
-      <c r="AV32" s="45" t="inlineStr"/>
+      <c r="AU32" s="10" t="n"/>
+      <c r="AV32" s="10" t="n"/>
       <c r="AW32" s="10" t="n"/>
-      <c r="AX32" s="11" t="n"/>
-      <c r="AY32" s="45" t="inlineStr"/>
+      <c r="AX32" s="10" t="n"/>
+      <c r="AY32" s="10" t="n"/>
       <c r="AZ32" s="10" t="n"/>
-      <c r="BA32" s="11" t="n"/>
-      <c r="BB32" s="45" t="inlineStr"/>
+      <c r="BA32" s="10" t="n"/>
+      <c r="BB32" s="10" t="n"/>
       <c r="BC32" s="10" t="n"/>
-      <c r="BD32" s="11" t="n"/>
-      <c r="BE32" s="45" t="inlineStr"/>
+      <c r="BD32" s="10" t="n"/>
+      <c r="BE32" s="10" t="n"/>
       <c r="BF32" s="10" t="n"/>
-      <c r="BG32" s="11" t="n"/>
-      <c r="BH32" s="45" t="inlineStr"/>
+      <c r="BG32" s="10" t="n"/>
+      <c r="BH32" s="10" t="n"/>
       <c r="BI32" s="10" t="n"/>
-      <c r="BJ32" s="11" t="n"/>
-      <c r="BK32" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ32" s="10" t="n"/>
+      <c r="BK32" s="10" t="n"/>
       <c r="BL32" s="10" t="n"/>
       <c r="BM32" s="10" t="n"/>
       <c r="BN32" s="10" t="n"/>
@@ -10335,74 +10278,161 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>入力バリデーション（Input Validation）</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n"/>
+    <row r="33" ht="176" customHeight="1">
+      <c r="A33" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-018</t>
+        </is>
+      </c>
       <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>対象JA未選択での必須チェック</t>
+        </is>
+      </c>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済</t>
+        </is>
+      </c>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">対象JAを1件も追加せず、ファイルと削除予定日のみ入力して「アップロード実行」を押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevToolsで対象JAを空にした状態で POST `/api/v1/file-upload` を直接送信</t>
+          </r>
+        </is>
+      </c>
       <c r="R33" s="10" t="n"/>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="10" t="n"/>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・必須入力エラーが表示されること（メッセージ `必須項目です。`、ACSMS-MSG-023-001）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>HTTPステータスコード400が返却されること（`error_code: TARGET_JA_REQUIRED`、メッセージ `対象JAを1つ以上選択してください。`）</t>
+          </r>
+        </is>
+      </c>
       <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="10" t="n"/>
       <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="10" t="n"/>
-      <c r="AF33" s="10" t="n"/>
-      <c r="AG33" s="10" t="n"/>
+      <c r="AD33" s="11" t="n"/>
+      <c r="AE33" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF33" s="11" t="n"/>
+      <c r="AG33" s="45" t="inlineStr"/>
       <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
+      <c r="AI33" s="11" t="n"/>
+      <c r="AJ33" s="45" t="inlineStr"/>
       <c r="AK33" s="10" t="n"/>
-      <c r="AL33" s="10" t="n"/>
-      <c r="AM33" s="10" t="n"/>
+      <c r="AL33" s="11" t="n"/>
+      <c r="AM33" s="45" t="inlineStr"/>
       <c r="AN33" s="10" t="n"/>
-      <c r="AO33" s="10" t="n"/>
-      <c r="AP33" s="10" t="n"/>
+      <c r="AO33" s="11" t="n"/>
+      <c r="AP33" s="45" t="inlineStr"/>
       <c r="AQ33" s="10" t="n"/>
-      <c r="AR33" s="10" t="n"/>
-      <c r="AS33" s="10" t="n"/>
+      <c r="AR33" s="11" t="n"/>
+      <c r="AS33" s="45" t="inlineStr"/>
       <c r="AT33" s="10" t="n"/>
-      <c r="AU33" s="10" t="n"/>
-      <c r="AV33" s="10" t="n"/>
+      <c r="AU33" s="11" t="n"/>
+      <c r="AV33" s="45" t="inlineStr"/>
       <c r="AW33" s="10" t="n"/>
-      <c r="AX33" s="10" t="n"/>
-      <c r="AY33" s="10" t="n"/>
+      <c r="AX33" s="11" t="n"/>
+      <c r="AY33" s="45" t="inlineStr"/>
       <c r="AZ33" s="10" t="n"/>
-      <c r="BA33" s="10" t="n"/>
-      <c r="BB33" s="10" t="n"/>
+      <c r="BA33" s="11" t="n"/>
+      <c r="BB33" s="45" t="inlineStr"/>
       <c r="BC33" s="10" t="n"/>
-      <c r="BD33" s="10" t="n"/>
-      <c r="BE33" s="10" t="n"/>
+      <c r="BD33" s="11" t="n"/>
+      <c r="BE33" s="45" t="inlineStr"/>
       <c r="BF33" s="10" t="n"/>
-      <c r="BG33" s="10" t="n"/>
-      <c r="BH33" s="10" t="n"/>
+      <c r="BG33" s="11" t="n"/>
+      <c r="BH33" s="45" t="inlineStr"/>
       <c r="BI33" s="10" t="n"/>
-      <c r="BJ33" s="10" t="n"/>
-      <c r="BK33" s="10" t="n"/>
+      <c r="BJ33" s="11" t="n"/>
+      <c r="BK33" s="46" t="inlineStr"/>
       <c r="BL33" s="10" t="n"/>
       <c r="BM33" s="10" t="n"/>
       <c r="BN33" s="10" t="n"/>
@@ -10423,7 +10453,7 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="46" t="inlineStr">
         <is>
-          <t>対象JA未選択での必須チェック</t>
+          <t>同一JAの重複追加チェック</t>
         </is>
       </c>
       <c r="F34" s="10" t="n"/>
@@ -10458,7 +10488,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAを1件も追加せず、ファイルと削除予定日のみ入力して「アップロード実行」を押下
+            <t xml:space="preserve">対象JAで1件のJAを選択し「追加」ボタンを押下
 </t>
           </r>
           <r>
@@ -10475,7 +10505,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsで対象JAを空にした状態で POST `/api/v1/file-upload` を直接送信</t>
+            <t>同一のJAを再度選択し「追加」ボタンを押下</t>
           </r>
         </is>
       </c>
@@ -10501,7 +10531,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・必須入力エラーが表示されること（メッセージ `必須項目です。`、ACSMS-MSG-023-001）
+            <t xml:space="preserve">・選択したJAがJA一覧に追加されること（JAコード＋JA名）
 </t>
           </r>
           <r>
@@ -10518,7 +10548,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: TARGET_JA_REQUIRED`、メッセージ `対象JAを1つ以上選択してください。`）</t>
+            <t xml:space="preserve">・エラーメッセージ `このJAは既に選択されています。`（ACSMS-MSG-023-004）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・JA一覧に重複データが追加されないこと</t>
           </r>
         </is>
       </c>
@@ -10572,7 +10610,7 @@
       <c r="BP34" s="10" t="n"/>
       <c r="BQ34" s="11" t="n"/>
     </row>
-    <row r="35" ht="176" customHeight="1">
+    <row r="35" ht="96" customHeight="1">
       <c r="A35" s="44" t="n">
         <v>20</v>
       </c>
@@ -10585,7 +10623,7 @@
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="46" t="inlineStr">
         <is>
-          <t>同一JAの重複追加チェック</t>
+          <t>ファイル未選択での必須チェック</t>
         </is>
       </c>
       <c r="F35" s="10" t="n"/>
@@ -10620,24 +10658,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAで1件のJAを選択し「追加」ボタンを押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>同一のJAを再度選択し「追加」ボタンを押下</t>
+            <t>対象JAと削除予定日のみ入力し、ファイルを1件も選択せず「アップロード実行」を押下</t>
           </r>
         </is>
       </c>
@@ -10663,32 +10684,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・選択したJAがJA一覧に追加されること（JAコード＋JA名）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・エラーメッセージ `このJAは既に選択されています。`（ACSMS-MSG-023-004）が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・JA一覧に重複データが追加されないこと</t>
+            <t xml:space="preserve">・必須入力エラーが表示されること（メッセージ `必須項目です。`、ACSMS-MSG-023-001）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・アップロード処理が実行されないこと</t>
           </r>
         </is>
       </c>
@@ -10755,7 +10759,7 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>ファイル未選択での必須チェック</t>
+          <t>削除予定日未入力での必須チェック</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -10790,7 +10794,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>対象JAと削除予定日のみ入力し、ファイルを1件も選択せず「アップロード実行」を押下</t>
+            <t>対象JAとファイルのみ入力し、削除予定日を未入力のまま「アップロード実行」を押下</t>
           </r>
         </is>
       </c>
@@ -10878,7 +10882,7 @@
       <c r="BP36" s="10" t="n"/>
       <c r="BQ36" s="11" t="n"/>
     </row>
-    <row r="37" ht="96" customHeight="1">
+    <row r="37" ht="80" customHeight="1">
       <c r="A37" s="44" t="n">
         <v>22</v>
       </c>
@@ -10891,7 +10895,7 @@
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="46" t="inlineStr">
         <is>
-          <t>削除予定日未入力での必須チェック</t>
+          <t>削除予定日に過去日を選択（不可）</t>
         </is>
       </c>
       <c r="F37" s="10" t="n"/>
@@ -10926,7 +10930,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>対象JAとファイルのみ入力し、削除予定日を未入力のまま「アップロード実行」を押下</t>
+            <t>削除予定日のカレンダーで過去日（前日）を選択</t>
           </r>
         </is>
       </c>
@@ -10952,15 +10956,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・必須入力エラーが表示されること（メッセージ `必須項目です。`、ACSMS-MSG-023-001）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・アップロード処理が実行されないこと</t>
+            <t>・過去日が選択できないこと（カレンダー上で過去日が非活性、または選択時にエラーとなること）</t>
           </r>
         </is>
       </c>
@@ -11014,7 +11010,7 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="80" customHeight="1">
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="44" t="n">
         <v>23</v>
       </c>
@@ -11027,7 +11023,7 @@
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="46" t="inlineStr">
         <is>
-          <t>削除予定日に過去日を選択（不可）</t>
+          <t>削除予定日に当日を選択（境界値・許可）</t>
         </is>
       </c>
       <c r="F38" s="10" t="n"/>
@@ -11062,7 +11058,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>削除予定日のカレンダーで過去日（前日）を選択</t>
+            <t>削除予定日のカレンダーで当日を選択</t>
           </r>
         </is>
       </c>
@@ -11088,7 +11084,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・過去日が選択できないこと（カレンダー上で過去日が非活性、または選択時にエラーとなること）</t>
+            <t>・当日が選択可能であること（境界値として許可されること）</t>
           </r>
         </is>
       </c>
@@ -11100,7 +11096,7 @@
       <c r="AD38" s="11" t="n"/>
       <c r="AE38" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF38" s="11" t="n"/>
@@ -11134,7 +11130,11 @@
       <c r="BH38" s="45" t="inlineStr"/>
       <c r="BI38" s="10" t="n"/>
       <c r="BJ38" s="11" t="n"/>
-      <c r="BK38" s="46" t="inlineStr"/>
+      <c r="BK38" s="46" t="inlineStr">
+        <is>
+          <t>過去日不可の境界（当日は許可）。仕様上の境界確認のため当日扱いを顧客と確認すること。</t>
+        </is>
+      </c>
       <c r="BL38" s="10" t="n"/>
       <c r="BM38" s="10" t="n"/>
       <c r="BN38" s="10" t="n"/>
@@ -11142,7 +11142,7 @@
       <c r="BP38" s="10" t="n"/>
       <c r="BQ38" s="11" t="n"/>
     </row>
-    <row r="39" ht="48" customHeight="1">
+    <row r="39" ht="224" customHeight="1">
       <c r="A39" s="44" t="n">
         <v>24</v>
       </c>
@@ -11155,7 +11155,7 @@
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>削除予定日に当日を選択（境界値・許可）</t>
+          <t>ファイルサイズ30MB超過</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -11165,7 +11165,8 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
+・ログイン済 + MFA認証済
+・サイズ30MB超のテストファイルを用意</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -11190,7 +11191,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>削除予定日のカレンダーで当日を選択</t>
+            <t xml:space="preserve">30MBを超えるファイルを選択
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevToolsで30MB超のファイルを含む POST `/api/v1/file-upload` を直接送信</t>
           </r>
         </is>
       </c>
@@ -11216,7 +11234,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・当日が選択可能であること（境界値として許可されること）</t>
+            <t xml:space="preserve">・エラーメッセージ `ファイルサイズが30MBを超えています。({fileName})`（ACSMS-MSG-023-002）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・当該ファイルがファイル一覧に追加されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>HTTPステータスコード400が返却されること（`error_code: FILE_SIZE_EXCEEDED`、メッセージ `ファイルサイズが30MBを超えています。`）</t>
           </r>
         </is>
       </c>
@@ -11228,7 +11271,7 @@
       <c r="AD39" s="11" t="n"/>
       <c r="AE39" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF39" s="11" t="n"/>
@@ -11262,11 +11305,7 @@
       <c r="BH39" s="45" t="inlineStr"/>
       <c r="BI39" s="10" t="n"/>
       <c r="BJ39" s="11" t="n"/>
-      <c r="BK39" s="46" t="inlineStr">
-        <is>
-          <t>過去日不可の境界（当日は許可）。仕様上の境界確認のため当日扱いを顧客と確認すること。</t>
-        </is>
-      </c>
+      <c r="BK39" s="46" t="inlineStr"/>
       <c r="BL39" s="10" t="n"/>
       <c r="BM39" s="10" t="n"/>
       <c r="BN39" s="10" t="n"/>
@@ -11274,7 +11313,7 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="224" customHeight="1">
+    <row r="40" ht="80" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
@@ -11287,7 +11326,7 @@
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>ファイルサイズ30MB超過</t>
+          <t>ファイルサイズ30MBちょうど（境界値・許可）</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -11298,7 +11337,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・サイズ30MB超のテストファイルを用意</t>
+・サイズちょうど30MB（30×1024×1024バイト）のテストファイルを用意</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -11323,24 +11362,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">30MBを超えるファイルを選択
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DevToolsで30MB超のファイルを含む POST `/api/v1/file-upload` を直接送信</t>
+            <t>ちょうど30MBのファイルを選択</t>
           </r>
         </is>
       </c>
@@ -11366,32 +11388,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・エラーメッセージ `ファイルサイズが30MBを超えています。({fileName})`（ACSMS-MSG-023-002）が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・当該ファイルがファイル一覧に追加されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: FILE_SIZE_EXCEEDED`、メッセージ `ファイルサイズが30MBを超えています。`）</t>
+            <t>・ファイルがファイル一覧に追加されること（境界値として許可されること）</t>
           </r>
         </is>
       </c>
@@ -11403,7 +11400,7 @@
       <c r="AD40" s="11" t="n"/>
       <c r="AE40" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF40" s="11" t="n"/>
@@ -11445,7 +11442,7 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="80" customHeight="1">
+    <row r="41" ht="112" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
@@ -11458,7 +11455,7 @@
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>ファイルサイズ30MBちょうど（境界値・許可）</t>
+          <t>許可形式ファイルの受理</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -11469,7 +11466,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・サイズちょうど30MB（30×1024×1024バイト）のテストファイルを用意</t>
+・各許可拡張子（.xlsx, .xls, .pdf, .jpg, .jpeg, .png, .doc, .docx, .pptx, .ppt, .csv, .txt, .zip）のテストファイルを用意</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -11494,7 +11491,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>ちょうど30MBのファイルを選択</t>
+            <t>許可拡張子のファイルを順に選択</t>
           </r>
         </is>
       </c>
@@ -11520,7 +11517,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・ファイルがファイル一覧に追加されること（境界値として許可されること）</t>
+            <t>・許可拡張子（Excel／PDF／画像／Word／PowerPoint／CSV／テキスト／圧縮）のファイルがファイル一覧に追加されること</t>
           </r>
         </is>
       </c>
@@ -11532,7 +11529,7 @@
       <c r="AD41" s="11" t="n"/>
       <c r="AE41" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF41" s="11" t="n"/>
@@ -11574,7 +11571,7 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="112" customHeight="1">
+    <row r="42" ht="224" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
@@ -11587,7 +11584,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>許可形式ファイルの受理</t>
+          <t>非許可形式ファイルの拒否</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -11598,7 +11595,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・各許可拡張子（.xlsx, .xls, .pdf, .jpg, .jpeg, .png, .doc, .docx, .pptx, .ppt, .csv, .txt, .zip）のテストファイルを用意</t>
+・非許可拡張子（.exe）のテストファイルを用意</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -11623,7 +11620,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>許可拡張子のファイルを順に選択</t>
+            <t xml:space="preserve">非許可拡張子（.exe）のファイルを選択
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevToolsで非許可拡張子のファイルを含む POST `/api/v1/file-upload` を直接送信</t>
           </r>
         </is>
       </c>
@@ -11649,7 +11663,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・許可拡張子（Excel／PDF／画像／Word／PowerPoint／CSV／テキスト／圧縮）のファイルがファイル一覧に追加されること</t>
+            <t xml:space="preserve">・エラーメッセージ `許可されていないファイル形式です。({fileName})`（ACSMS-MSG-023-010）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・当該ファイルがファイル一覧に追加されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>HTTPステータスコード400が返却されること（`error_code: FILE_FORMAT_ERROR`、メッセージ `許可されていないファイル形式です。`）</t>
           </r>
         </is>
       </c>
@@ -11661,7 +11700,7 @@
       <c r="AD42" s="11" t="n"/>
       <c r="AE42" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -11703,7 +11742,7 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="224" customHeight="1">
+    <row r="43" ht="80" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>28</v>
       </c>
@@ -11716,7 +11755,7 @@
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="46" t="inlineStr">
         <is>
-          <t>非許可形式ファイルの拒否</t>
+          <t>大文字拡張子の受理（小文字化判定）</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -11727,7 +11766,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・非許可拡張子（.exe）のテストファイルを用意</t>
+・大文字拡張子のテストファイル（`IMG.JPG`）を用意</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -11752,24 +11791,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">非許可拡張子（.exe）のファイルを選択
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DevToolsで非許可拡張子のファイルを含む POST `/api/v1/file-upload` を直接送信</t>
+            <t>大文字拡張子のファイル（`IMG.JPG`）を選択</t>
           </r>
         </is>
       </c>
@@ -11795,32 +11817,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・エラーメッセージ `許可されていないファイル形式です。({fileName})`（ACSMS-MSG-023-010）が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・当該ファイルがファイル一覧に追加されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: FILE_FORMAT_ERROR`、メッセージ `許可されていないファイル形式です。`）</t>
+            <t>・ファイルがファイル一覧に追加されること（拡張子は小文字化して判定されるため、`.JPG` も許可されること）</t>
           </r>
         </is>
       </c>
@@ -11832,7 +11829,7 @@
       <c r="AD43" s="11" t="n"/>
       <c r="AE43" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF43" s="11" t="n"/>
@@ -11874,7 +11871,7 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="80" customHeight="1">
+    <row r="44" ht="144" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>29</v>
       </c>
@@ -11887,7 +11884,7 @@
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="46" t="inlineStr">
         <is>
-          <t>大文字拡張子の受理（小文字化判定）</t>
+          <t>複数ファイル選択とファイル名形式の表示</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -11897,8 +11894,7 @@
       <c r="J44" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・大文字拡張子のテストファイル（`IMG.JPG`）を用意</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
@@ -11923,7 +11919,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>大文字拡張子のファイル（`IMG.JPG`）を選択</t>
+            <t xml:space="preserve">複数ファイルを同時に選択
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>アップロード後、「アップロードされたファイルリスト」のファイル名表示形式を確認</t>
           </r>
         </is>
       </c>
@@ -11949,7 +11962,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・ファイルがファイル一覧に追加されること（拡張子は小文字化して判定されるため、`.JPG` も許可されること）</t>
+            <t xml:space="preserve">・複数ファイルがすべてファイル一覧に追加されること（ファイル名＋サイズ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ファイル名が「yyyymmddJaIDRole_ファイル名」の形式で表示されること</t>
           </r>
         </is>
       </c>
@@ -11961,7 +11991,7 @@
       <c r="AD44" s="11" t="n"/>
       <c r="AE44" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF44" s="11" t="n"/>
@@ -11995,7 +12025,12 @@
       <c r="BH44" s="45" t="inlineStr"/>
       <c r="BI44" s="10" t="n"/>
       <c r="BJ44" s="11" t="n"/>
-      <c r="BK44" s="46" t="inlineStr"/>
+      <c r="BK44" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL44" s="10" t="n"/>
       <c r="BM44" s="10" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -12003,166 +12038,74 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="144" customHeight="1">
-      <c r="A45" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="B45" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-030</t>
-        </is>
-      </c>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック — アップロード（Function — Upload）</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="46" t="inlineStr">
-        <is>
-          <t>複数ファイル選択とファイル名形式の表示</t>
-        </is>
-      </c>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="11" t="n"/>
-      <c r="Q45" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">複数ファイルを同時に選択
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>アップロード後、「アップロードされたファイルリスト」のファイル名表示形式を確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
       <c r="R45" s="10" t="n"/>
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
-      <c r="W45" s="11" t="n"/>
-      <c r="X45" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・複数ファイルがすべてファイル一覧に追加されること（ファイル名＋サイズ）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・ファイル名が「yyyymmddJaIDRole_ファイル名」の形式で表示されること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
       <c r="Y45" s="10" t="n"/>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="10" t="n"/>
       <c r="AC45" s="10" t="n"/>
-      <c r="AD45" s="11" t="n"/>
-      <c r="AE45" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF45" s="11" t="n"/>
-      <c r="AG45" s="45" t="inlineStr"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
       <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="11" t="n"/>
-      <c r="AJ45" s="45" t="inlineStr"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="10" t="n"/>
-      <c r="AL45" s="11" t="n"/>
-      <c r="AM45" s="45" t="inlineStr"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="10" t="n"/>
       <c r="AN45" s="10" t="n"/>
-      <c r="AO45" s="11" t="n"/>
-      <c r="AP45" s="45" t="inlineStr"/>
+      <c r="AO45" s="10" t="n"/>
+      <c r="AP45" s="10" t="n"/>
       <c r="AQ45" s="10" t="n"/>
-      <c r="AR45" s="11" t="n"/>
-      <c r="AS45" s="45" t="inlineStr"/>
+      <c r="AR45" s="10" t="n"/>
+      <c r="AS45" s="10" t="n"/>
       <c r="AT45" s="10" t="n"/>
-      <c r="AU45" s="11" t="n"/>
-      <c r="AV45" s="45" t="inlineStr"/>
+      <c r="AU45" s="10" t="n"/>
+      <c r="AV45" s="10" t="n"/>
       <c r="AW45" s="10" t="n"/>
-      <c r="AX45" s="11" t="n"/>
-      <c r="AY45" s="45" t="inlineStr"/>
+      <c r="AX45" s="10" t="n"/>
+      <c r="AY45" s="10" t="n"/>
       <c r="AZ45" s="10" t="n"/>
-      <c r="BA45" s="11" t="n"/>
-      <c r="BB45" s="45" t="inlineStr"/>
+      <c r="BA45" s="10" t="n"/>
+      <c r="BB45" s="10" t="n"/>
       <c r="BC45" s="10" t="n"/>
-      <c r="BD45" s="11" t="n"/>
-      <c r="BE45" s="45" t="inlineStr"/>
+      <c r="BD45" s="10" t="n"/>
+      <c r="BE45" s="10" t="n"/>
       <c r="BF45" s="10" t="n"/>
-      <c r="BG45" s="11" t="n"/>
-      <c r="BH45" s="45" t="inlineStr"/>
+      <c r="BG45" s="10" t="n"/>
+      <c r="BH45" s="10" t="n"/>
       <c r="BI45" s="10" t="n"/>
-      <c r="BJ45" s="11" t="n"/>
-      <c r="BK45" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ45" s="10" t="n"/>
+      <c r="BK45" s="10" t="n"/>
       <c r="BL45" s="10" t="n"/>
       <c r="BM45" s="10" t="n"/>
       <c r="BN45" s="10" t="n"/>
@@ -12170,74 +12113,236 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="32" t="inlineStr">
-        <is>
-          <t>業務ロジック — アップロード（Function — Upload）</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
+    <row r="46" ht="448" customHeight="1">
+      <c r="A46" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-030</t>
+        </is>
+      </c>
       <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>アップロード正常系（単一JA×単一ファイル）</t>
+        </is>
+      </c>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済</t>
+        </is>
+      </c>
       <c r="K46" s="10" t="n"/>
       <c r="L46" s="10" t="n"/>
       <c r="M46" s="10" t="n"/>
       <c r="N46" s="10" t="n"/>
       <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">対象JAを1件追加し、許可形式のファイルを1件選択、削除予定日を当日以降で入力
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「アップロード実行」を押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>確認ダイアログで「OK」を押下</t>
+          </r>
+        </is>
+      </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
+      <c r="W46" s="11" t="n"/>
+      <c r="X46" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・対象JAとファイルが一覧に表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルをアップロードしますか？`、ACSMS-MSG-023-008）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・HTTPステータスコード202が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・成功メッセージ `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・フォーム（対象JA・ファイル・削除予定日）がクリアされること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「アップロードされたファイルリスト」が再取得され、新規行が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新規行の「通知ステータス」列に「未送信」または「送信中」バッジが表示されること</t>
+          </r>
+        </is>
+      </c>
       <c r="Y46" s="10" t="n"/>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="10" t="n"/>
       <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+      <c r="AE46" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF46" s="11" t="n"/>
+      <c r="AG46" s="45" t="inlineStr"/>
       <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
+      <c r="AI46" s="11" t="n"/>
+      <c r="AJ46" s="45" t="inlineStr"/>
       <c r="AK46" s="10" t="n"/>
-      <c r="AL46" s="10" t="n"/>
-      <c r="AM46" s="10" t="n"/>
+      <c r="AL46" s="11" t="n"/>
+      <c r="AM46" s="45" t="inlineStr"/>
       <c r="AN46" s="10" t="n"/>
-      <c r="AO46" s="10" t="n"/>
-      <c r="AP46" s="10" t="n"/>
+      <c r="AO46" s="11" t="n"/>
+      <c r="AP46" s="45" t="inlineStr"/>
       <c r="AQ46" s="10" t="n"/>
-      <c r="AR46" s="10" t="n"/>
-      <c r="AS46" s="10" t="n"/>
+      <c r="AR46" s="11" t="n"/>
+      <c r="AS46" s="45" t="inlineStr"/>
       <c r="AT46" s="10" t="n"/>
-      <c r="AU46" s="10" t="n"/>
-      <c r="AV46" s="10" t="n"/>
+      <c r="AU46" s="11" t="n"/>
+      <c r="AV46" s="45" t="inlineStr"/>
       <c r="AW46" s="10" t="n"/>
-      <c r="AX46" s="10" t="n"/>
-      <c r="AY46" s="10" t="n"/>
+      <c r="AX46" s="11" t="n"/>
+      <c r="AY46" s="45" t="inlineStr"/>
       <c r="AZ46" s="10" t="n"/>
-      <c r="BA46" s="10" t="n"/>
-      <c r="BB46" s="10" t="n"/>
+      <c r="BA46" s="11" t="n"/>
+      <c r="BB46" s="45" t="inlineStr"/>
       <c r="BC46" s="10" t="n"/>
-      <c r="BD46" s="10" t="n"/>
-      <c r="BE46" s="10" t="n"/>
+      <c r="BD46" s="11" t="n"/>
+      <c r="BE46" s="45" t="inlineStr"/>
       <c r="BF46" s="10" t="n"/>
-      <c r="BG46" s="10" t="n"/>
-      <c r="BH46" s="10" t="n"/>
+      <c r="BG46" s="11" t="n"/>
+      <c r="BH46" s="45" t="inlineStr"/>
       <c r="BI46" s="10" t="n"/>
-      <c r="BJ46" s="10" t="n"/>
-      <c r="BK46" s="10" t="n"/>
+      <c r="BJ46" s="11" t="n"/>
+      <c r="BK46" s="46" t="inlineStr"/>
       <c r="BL46" s="10" t="n"/>
       <c r="BM46" s="10" t="n"/>
       <c r="BN46" s="10" t="n"/>
@@ -12245,7 +12350,7 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="448" customHeight="1">
+    <row r="47" ht="208" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>31</v>
       </c>
@@ -12258,7 +12363,7 @@
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>アップロード正常系（単一JA×単一ファイル）</t>
+          <t>N×M レコード生成（複数JA×複数ファイル）</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -12293,7 +12398,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAを1件追加し、許可形式のファイルを1件選択、削除予定日を当日以降で入力
+            <t xml:space="preserve">対象JAを2件追加し、許可形式のファイルを2件選択、削除予定日を入力して「アップロード実行」→「OK」を押下
 </t>
           </r>
           <r>
@@ -12310,24 +12415,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「アップロード実行」を押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>確認ダイアログで「OK」を押下</t>
+            <t>DB確認: `SELECT ja_id, file_name FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 4`</t>
           </r>
         </is>
       </c>
@@ -12353,7 +12441,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・対象JAとファイルが一覧に表示されること
+            <t xml:space="preserve">・HTTPステータスコード202が返却されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・成功メッセージ `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）が表示されること
 </t>
           </r>
           <r>
@@ -12370,65 +12466,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルをアップロードしますか？`、ACSMS-MSG-023-008）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・HTTPステータスコード202が返却されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・成功メッセージ `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・フォーム（対象JA・ファイル・削除予定日）がクリアされること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「アップロードされたファイルリスト」が再取得され、新規行が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・新規行の「通知ステータス」列に「未送信」または「送信中」バッジが表示されること</t>
+            <t>・`t_file_upload` に N×M = 2×2 = 4 件のレコードが登録されること（各JA×各ファイルの組み合わせ）</t>
           </r>
         </is>
       </c>
@@ -12482,7 +12520,7 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="208" customHeight="1">
+    <row r="48" ht="176" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>32</v>
       </c>
@@ -12495,7 +12533,7 @@
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>N×M レコード生成（複数JA×複数ファイル）</t>
+          <t>全JA選択（ja_id=NULL のレコード）</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -12530,7 +12568,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAを2件追加し、許可形式のファイルを2件選択、削除予定日を入力して「アップロード実行」→「OK」を押下
+            <t xml:space="preserve">対象JAで「全JA」を選択して追加し、ファイルを1件選択、削除予定日を入力して「アップロード実行」→「OK」を押下
 </t>
           </r>
           <r>
@@ -12547,7 +12585,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT ja_id, file_name FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 4`</t>
+            <t>DB確認: `SELECT ja_id FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -12579,14 +12617,6 @@
           <r>
             <rPr>
               <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・成功メッセージ `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
               <b val="1"/>
               <sz val="10"/>
             </rPr>
@@ -12598,7 +12628,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`t_file_upload` に N×M = 2×2 = 4 件のレコードが登録されること（各JA×各ファイルの組み合わせ）</t>
+            <t>・`t_file_upload` に `ja_id` が NULL のレコードが1件登録されること</t>
           </r>
         </is>
       </c>
@@ -12652,7 +12682,7 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="176" customHeight="1">
+    <row r="49" ht="192" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>33</v>
       </c>
@@ -12665,7 +12695,7 @@
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>全JA選択（ja_id=NULL のレコード）</t>
+          <t>DB永続化と初期ステータスの確認</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -12700,7 +12730,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAで「全JA」を選択して追加し、ファイルを1件選択、削除予定日を入力して「アップロード実行」→「OK」を押下
+            <t xml:space="preserve">アップロードを実行する（単一JA×単一ファイル）
 </t>
           </r>
           <r>
@@ -12717,7 +12747,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT ja_id FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 1`</t>
+            <t>DB確認: `SELECT status, notification_status, scheduled_delete_date, error_file_path FROM t_file_upload WHERE file_upload_id = :new_id`</t>
           </r>
         </is>
       </c>
@@ -12760,7 +12790,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`t_file_upload` に `ja_id` が NULL のレコードが1件登録されること</t>
+            <t xml:space="preserve">・データが登録されること（`status = 1`（処理中）、`notification_status = 1`（未送信）、`error_file_path = ""`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`scheduled_delete_date` が画面で指定した削除予定日で登録されること</t>
           </r>
         </is>
       </c>
@@ -12827,7 +12865,7 @@
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>DB永続化と初期ステータスの確認</t>
+          <t>監査ログの記録（アップロード）</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -12862,7 +12900,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">アップロードを実行する（単一JA×単一ファイル）
+            <t xml:space="preserve">アップロードを実行する
 </t>
           </r>
           <r>
@@ -12879,7 +12917,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT status, notification_status, scheduled_delete_date, error_file_path FROM t_file_upload WHERE file_upload_id = :new_id`</t>
+            <t>DB確認: `SELECT log_type, operation, result_status, target_table, account_id FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -12922,15 +12960,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・データが登録されること（`status = 1`（処理中）、`notification_status = 1`（未送信）、`error_file_path = ""`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`scheduled_delete_date` が画面で指定した削除予定日で登録されること</t>
+            <t xml:space="preserve">・監査ログが記録されること（`log_type = 4`（ファイル操作）、`operation = 'CREATE'`、`result_status = 1`、`target_table = 't_file_upload'`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`account_id` がテストアカウントと一致すること</t>
           </r>
         </is>
       </c>
@@ -12984,7 +13022,7 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="192" customHeight="1">
+    <row r="51" ht="272" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>35</v>
       </c>
@@ -12997,7 +13035,7 @@
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>監査ログの記録（アップロード）</t>
+          <t>通知ステータスバッジの遷移（非同期）</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -13007,7 +13045,8 @@
       <c r="J51" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
+・ログイン済 + MFA認証済
+・対象JAに通知先メールアドレス（`m_account.email` 等）が設定済み</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -13032,7 +13071,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">アップロードを実行する
+            <t xml:space="preserve">アップロードを実行し、「アップロードされたファイルリスト」の「通知ステータス」列を確認
 </t>
           </r>
           <r>
@@ -13049,7 +13088,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT log_type, operation, result_status, target_table, account_id FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>一定時間後（バックグラウンドワーカーの処理後）、画面を再読み込みし「通知ステータス」列を再確認</t>
           </r>
         </is>
       </c>
@@ -13075,7 +13114,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード202が返却されること
+            <t xml:space="preserve">・「通知ステータス」列に「未送信」または「送信中」バッジが表示されること
 </t>
           </r>
           <r>
@@ -13092,15 +13131,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・監査ログが記録されること（`log_type = 4`（ファイル操作）、`operation = 'CREATE'`、`result_status = 1`、`target_table = 't_file_upload'`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`account_id` がテストアカウントと一致すること</t>
+            <t xml:space="preserve">・全アドレス送信成功後、「通知ステータス」が「完了」バッジに更新されること（`notification_status = 3`、`notified_at` が記録されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・メール送信はバックグラウンドワーカーが非同期で実行するため、APIは即時に HTTP 202 を返却すること</t>
           </r>
         </is>
       </c>
@@ -13154,7 +13202,7 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="272" customHeight="1">
+    <row r="52" ht="288" customHeight="1">
       <c r="A52" s="44" t="n">
         <v>36</v>
       </c>
@@ -13167,7 +13215,7 @@
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="46" t="inlineStr">
         <is>
-          <t>通知ステータスバッジの遷移（非同期）</t>
+          <t>一部のJAへの通知メール送信失敗</t>
         </is>
       </c>
       <c r="F52" s="10" t="n"/>
@@ -13178,7 +13226,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・対象JAに通知先メールアドレス（`m_account.email` 等）が設定済み</t>
+・複数JAのうち1件のメールアドレスが無効な状態を用意</t>
         </is>
       </c>
       <c r="K52" s="10" t="n"/>
@@ -13203,7 +13251,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">アップロードを実行し、「アップロードされたファイルリスト」の「通知ステータス」列を確認
+            <t xml:space="preserve">複数JAを対象にアップロードを実行する（1件は送信失敗する状態）
 </t>
           </r>
           <r>
@@ -13220,7 +13268,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>一定時間後（バックグラウンドワーカーの処理後）、画面を再読み込みし「通知ステータス」列を再確認</t>
+            <t>バックグラウンドワーカーの処理後、画面を再読み込みし「通知ステータス」列を確認</t>
           </r>
         </is>
       </c>
@@ -13246,7 +13294,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「通知ステータス」列に「未送信」または「送信中」バッジが表示されること
+            <t xml:space="preserve">・HTTPステータスコード202が返却されること
 </t>
           </r>
           <r>
@@ -13263,24 +13311,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・全アドレス送信成功後、「通知ステータス」が「完了」バッジに更新されること（`notification_status = 3`、`notified_at` が記録されること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・メール送信はバックグラウンドワーカーが非同期で実行するため、APIは即時に HTTP 202 を返却すること</t>
+            <t xml:space="preserve">・失敗したJAの行の「通知ステータス」が「一部失敗」バッジで表示されること（`notification_status = 4`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・メッセージ `一部のJAへの通知メール送信に失敗しました。「通知ステータス」が「一部失敗」の行をご確認ください。`（ACSMS-MSG-023-007）が確認できること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・エラーログ（`t_log`、`log_type = 3`）に失敗詳細が記録されること</t>
           </r>
         </is>
       </c>
@@ -13292,7 +13339,7 @@
       <c r="AD52" s="11" t="n"/>
       <c r="AE52" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF52" s="11" t="n"/>
@@ -13334,7 +13381,7 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="288" customHeight="1">
+    <row r="53" ht="240" customHeight="1">
       <c r="A53" s="44" t="n">
         <v>37</v>
       </c>
@@ -13347,7 +13394,7 @@
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>一部のJAへの通知メール送信失敗</t>
+          <t>確認ダイアログのキャンセル</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -13357,8 +13404,7 @@
       <c r="J53" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・複数JAのうち1件のメールアドレスが無効な状態を用意</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K53" s="10" t="n"/>
@@ -13383,7 +13429,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">複数JAを対象にアップロードを実行する（1件は送信失敗する状態）
+            <t xml:space="preserve">対象JAとファイル、削除予定日を入力し「アップロード実行」を押下
 </t>
           </r>
           <r>
@@ -13400,7 +13446,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>バックグラウンドワーカーの処理後、画面を再読み込みし「通知ステータス」列を確認</t>
+            <t xml:space="preserve">確認ダイアログ（ACSMS-MSG-023-008）で「キャンセル」を押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（押下前後で件数比較）</t>
           </r>
         </is>
       </c>
@@ -13426,7 +13489,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード202が返却されること
+            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルをアップロードしますか？`）
 </t>
           </r>
           <r>
@@ -13443,23 +13506,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・失敗したJAの行の「通知ステータス」が「一部失敗」バッジで表示されること（`notification_status = 4`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・メッセージ `一部のJAへの通知メール送信に失敗しました。「通知ステータス」が「一部失敗」の行をご確認ください。`（ACSMS-MSG-023-007）が確認できること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・エラーログ（`t_log`、`log_type = 3`）に失敗詳細が記録されること</t>
+            <t xml:space="preserve">・現在の画面が維持されること（入力内容が保持されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`t_file_upload` に新規データが登録されないこと</t>
           </r>
         </is>
       </c>
@@ -13513,7 +13577,7 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="240" customHeight="1">
+    <row r="54" ht="160" customHeight="1">
       <c r="A54" s="44" t="n">
         <v>38</v>
       </c>
@@ -13526,7 +13590,7 @@
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>確認ダイアログのキャンセル</t>
+          <t>クリアボタンによる選択解除</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -13561,7 +13625,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象JAとファイル、削除予定日を入力し「アップロード実行」を押下
+            <t xml:space="preserve">対象JAとファイルを選択した状態で「クリア」ボタンを押下
 </t>
           </r>
           <r>
@@ -13578,24 +13642,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">確認ダイアログ（ACSMS-MSG-023-008）で「キャンセル」を押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（押下前後で件数比較）</t>
+            <t>確認ダイアログで「OK」を押下</t>
           </r>
         </is>
       </c>
@@ -13621,7 +13668,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルをアップロードしますか？`）
+            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `全てのJAとファイルを削除します。よろしいでしょうか。`、ACSMS-MSG-023-003）
 </t>
           </r>
           <r>
@@ -13638,24 +13685,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・現在の画面が維持されること（入力内容が保持されること）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`t_file_upload` に新規データが登録されないこと</t>
+            <t>・選択したJA一覧およびファイル一覧がクリアされること</t>
           </r>
         </is>
       </c>
@@ -13667,7 +13697,7 @@
       <c r="AD54" s="11" t="n"/>
       <c r="AE54" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF54" s="11" t="n"/>
@@ -13701,7 +13731,12 @@
       <c r="BH54" s="45" t="inlineStr"/>
       <c r="BI54" s="10" t="n"/>
       <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BK54" s="46" t="inlineStr">
+        <is>
+          <t>「キャンセル」選択時は何も処理を行わないこと。
+---</t>
+        </is>
+      </c>
       <c r="BL54" s="10" t="n"/>
       <c r="BM54" s="10" t="n"/>
       <c r="BN54" s="10" t="n"/>
@@ -13709,166 +13744,74 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="160" customHeight="1">
-      <c r="A55" s="44" t="n">
-        <v>39</v>
-      </c>
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-039</t>
-        </is>
-      </c>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック — 削除（Function — Delete）</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="46" t="inlineStr">
-        <is>
-          <t>クリアボタンによる選択解除</t>
-        </is>
-      </c>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">対象JAとファイルを選択した状態で「クリア」ボタンを押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>確認ダイアログで「OK」を押下</t>
-          </r>
-        </is>
-      </c>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="10" t="n"/>
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="X55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `全てのJAとファイルを削除します。よろしいでしょうか。`、ACSMS-MSG-023-003）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・選択したJA一覧およびファイル一覧がクリアされること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="10" t="n"/>
       <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="11" t="n"/>
-      <c r="AE55" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF55" s="11" t="n"/>
-      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
       <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="11" t="n"/>
-      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="10" t="n"/>
-      <c r="AL55" s="11" t="n"/>
-      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AL55" s="10" t="n"/>
+      <c r="AM55" s="10" t="n"/>
       <c r="AN55" s="10" t="n"/>
-      <c r="AO55" s="11" t="n"/>
-      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AO55" s="10" t="n"/>
+      <c r="AP55" s="10" t="n"/>
       <c r="AQ55" s="10" t="n"/>
-      <c r="AR55" s="11" t="n"/>
-      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AR55" s="10" t="n"/>
+      <c r="AS55" s="10" t="n"/>
       <c r="AT55" s="10" t="n"/>
-      <c r="AU55" s="11" t="n"/>
-      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AU55" s="10" t="n"/>
+      <c r="AV55" s="10" t="n"/>
       <c r="AW55" s="10" t="n"/>
-      <c r="AX55" s="11" t="n"/>
-      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AX55" s="10" t="n"/>
+      <c r="AY55" s="10" t="n"/>
       <c r="AZ55" s="10" t="n"/>
-      <c r="BA55" s="11" t="n"/>
-      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BA55" s="10" t="n"/>
+      <c r="BB55" s="10" t="n"/>
       <c r="BC55" s="10" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BD55" s="10" t="n"/>
+      <c r="BE55" s="10" t="n"/>
       <c r="BF55" s="10" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BG55" s="10" t="n"/>
+      <c r="BH55" s="10" t="n"/>
       <c r="BI55" s="10" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="46" t="inlineStr">
-        <is>
-          <t>「キャンセル」選択時は何も処理を行わないこと。
----</t>
-        </is>
-      </c>
+      <c r="BJ55" s="10" t="n"/>
+      <c r="BK55" s="10" t="n"/>
       <c r="BL55" s="10" t="n"/>
       <c r="BM55" s="10" t="n"/>
       <c r="BN55" s="10" t="n"/>
@@ -13876,74 +13819,204 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="32" t="inlineStr">
-        <is>
-          <t>業務ロジック — ダウンロード・削除（Function — Download &amp; Delete）</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n"/>
+    <row r="56" ht="288" customHeight="1">
+      <c r="A56" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-039</t>
+        </is>
+      </c>
       <c r="C56" s="10" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>ファイル削除正常系（論理削除＋物理削除）</t>
+        </is>
+      </c>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済
+・削除対象ファイル（`deleted_at` が NULL）が存在</t>
+        </is>
+      </c>
       <c r="K56" s="10" t="n"/>
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="10" t="n"/>
       <c r="N56" s="10" t="n"/>
       <c r="O56" s="10" t="n"/>
-      <c r="P56" s="10" t="n"/>
-      <c r="Q56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「アップロードされたファイルリスト」で対象行の「削除」ボタンを押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">確認ダイアログで削除を確定
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB確認: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+          </r>
+        </is>
+      </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="10" t="n"/>
       <c r="T56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="10" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルを削除しますか？`、ACSMS-MSG-023-009）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・データが削除されること（メッセージ `削除しました。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・テーブルが更新され、削除した行の「削除日」列に削除日が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・論理削除されること（`deleted_at IS NOT NULL`）、かつ物理ファイルがストレージから削除されること</t>
+          </r>
+        </is>
+      </c>
       <c r="Y56" s="10" t="n"/>
       <c r="Z56" s="10" t="n"/>
       <c r="AA56" s="10" t="n"/>
       <c r="AB56" s="10" t="n"/>
       <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
-      <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="45" t="inlineStr"/>
       <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="45" t="inlineStr"/>
       <c r="AK56" s="10" t="n"/>
-      <c r="AL56" s="10" t="n"/>
-      <c r="AM56" s="10" t="n"/>
+      <c r="AL56" s="11" t="n"/>
+      <c r="AM56" s="45" t="inlineStr"/>
       <c r="AN56" s="10" t="n"/>
-      <c r="AO56" s="10" t="n"/>
-      <c r="AP56" s="10" t="n"/>
+      <c r="AO56" s="11" t="n"/>
+      <c r="AP56" s="45" t="inlineStr"/>
       <c r="AQ56" s="10" t="n"/>
-      <c r="AR56" s="10" t="n"/>
-      <c r="AS56" s="10" t="n"/>
+      <c r="AR56" s="11" t="n"/>
+      <c r="AS56" s="45" t="inlineStr"/>
       <c r="AT56" s="10" t="n"/>
-      <c r="AU56" s="10" t="n"/>
-      <c r="AV56" s="10" t="n"/>
+      <c r="AU56" s="11" t="n"/>
+      <c r="AV56" s="45" t="inlineStr"/>
       <c r="AW56" s="10" t="n"/>
-      <c r="AX56" s="10" t="n"/>
-      <c r="AY56" s="10" t="n"/>
+      <c r="AX56" s="11" t="n"/>
+      <c r="AY56" s="45" t="inlineStr"/>
       <c r="AZ56" s="10" t="n"/>
-      <c r="BA56" s="10" t="n"/>
-      <c r="BB56" s="10" t="n"/>
+      <c r="BA56" s="11" t="n"/>
+      <c r="BB56" s="45" t="inlineStr"/>
       <c r="BC56" s="10" t="n"/>
-      <c r="BD56" s="10" t="n"/>
-      <c r="BE56" s="10" t="n"/>
+      <c r="BD56" s="11" t="n"/>
+      <c r="BE56" s="45" t="inlineStr"/>
       <c r="BF56" s="10" t="n"/>
-      <c r="BG56" s="10" t="n"/>
-      <c r="BH56" s="10" t="n"/>
+      <c r="BG56" s="11" t="n"/>
+      <c r="BH56" s="45" t="inlineStr"/>
       <c r="BI56" s="10" t="n"/>
-      <c r="BJ56" s="10" t="n"/>
-      <c r="BK56" s="10" t="n"/>
+      <c r="BJ56" s="11" t="n"/>
+      <c r="BK56" s="46" t="inlineStr"/>
       <c r="BL56" s="10" t="n"/>
       <c r="BM56" s="10" t="n"/>
       <c r="BN56" s="10" t="n"/>
@@ -13951,7 +14024,7 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="224" customHeight="1">
+    <row r="57" ht="192" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>40</v>
       </c>
@@ -13964,7 +14037,7 @@
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>ファイルダウンロード正常系</t>
+          <t>監査ログの記録（削除）</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -13975,7 +14048,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・ダウンロード対象ファイル（`file_upload_id = 201`）が存在</t>
+・削除対象ファイルが存在</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -14000,7 +14073,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「アップロードされたファイルリスト」で対象ファイルのダウンロード操作を実行
+            <t xml:space="preserve">ファイルを削除する
 </t>
           </r>
           <r>
@@ -14017,7 +14090,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT download_type FROM t_file_download ORDER BY created_at DESC LIMIT 1` および `SELECT operation FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DOWNLOAD' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>DB確認: `SELECT log_type, operation, result_status, before_value FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DELETE' ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -14043,7 +14116,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード200が返却されること（Content-Disposition: `attachment; filename="..."`、ファイルのバイナリがダウンロードされること）
+            <t xml:space="preserve">・データが削除されること（メッセージ `削除しました。`）
 </t>
           </r>
           <r>
@@ -14060,15 +14133,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・`t_file_download` にダウンロード履歴が記録されること（`download_type = 2`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・監査ログが記録されること（`operation = 'DOWNLOAD'`、`log_type = 4`）</t>
+            <t xml:space="preserve">・監査ログが記録されること（`log_type = 4`、`operation = 'DELETE'`、`result_status = 1`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`before_value` に削除前のデータがJSON形式で記録されること</t>
           </r>
         </is>
       </c>
@@ -14122,7 +14195,7 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="288" customHeight="1">
+    <row r="58" ht="112" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>41</v>
       </c>
@@ -14135,7 +14208,7 @@
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>ファイル削除正常系（論理削除＋物理削除）</t>
+          <t>削除ボタンの活性／非活性制御</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -14146,7 +14219,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・削除対象ファイル（`deleted_at` が NULL）が存在</t>
+・`deleted_at` が NULL の行と NOT NULL の行が各1件以上存在</t>
         </is>
       </c>
       <c r="K58" s="10" t="n"/>
@@ -14171,41 +14244,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「アップロードされたファイルリスト」で対象行の「削除」ボタンを押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">確認ダイアログで削除を確定
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB確認: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+            <t>「アップロードされたファイルリスト」で各行の「削除」ボタンの状態を確認</t>
           </r>
         </is>
       </c>
@@ -14231,49 +14270,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルを削除しますか？`、ACSMS-MSG-023-009）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・データが削除されること（メッセージ `削除しました。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・テーブルが更新され、削除した行の「削除日」列に削除日が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・論理削除されること（`deleted_at IS NOT NULL`）、かつ物理ファイルがストレージから削除されること</t>
+            <t xml:space="preserve">・`deleted_at` が NULL の行は「削除」ボタンが活性状態で表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`deleted_at` が NOT NULL の行は「削除」ボタンが非活性状態で表示されること</t>
           </r>
         </is>
       </c>
@@ -14340,7 +14345,7 @@
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>監査ログの記録（削除）</t>
+          <t>削除確認ダイアログのキャンセル</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -14351,7 +14356,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・削除対象ファイルが存在</t>
+・削除対象ファイル（`deleted_at` が NULL）が存在</t>
         </is>
       </c>
       <c r="K59" s="10" t="n"/>
@@ -14376,7 +14381,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ファイルを削除する
+            <t xml:space="preserve">対象行の「削除」ボタンを押下
 </t>
           </r>
           <r>
@@ -14393,7 +14398,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT log_type, operation, result_status, before_value FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DELETE' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t xml:space="preserve">確認ダイアログ（ACSMS-MSG-023-009）で「キャンセル」を押下
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB確認: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
           </r>
         </is>
       </c>
@@ -14419,7 +14441,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・データが削除されること（メッセージ `削除しました。`）
+            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルを削除しますか？`）
 </t>
           </r>
           <r>
@@ -14436,15 +14458,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・監査ログが記録されること（`log_type = 4`、`operation = 'DELETE'`、`result_status = 1`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`before_value` に削除前のデータがJSON形式で記録されること</t>
+            <t xml:space="preserve">・現在の画面が維持されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・データが削除されないこと（`deleted_at IS NULL` のまま）</t>
           </r>
         </is>
       </c>
@@ -14456,7 +14487,7 @@
       <c r="AD59" s="11" t="n"/>
       <c r="AE59" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF59" s="11" t="n"/>
@@ -14490,7 +14521,12 @@
       <c r="BH59" s="45" t="inlineStr"/>
       <c r="BI59" s="10" t="n"/>
       <c r="BJ59" s="11" t="n"/>
-      <c r="BK59" s="46" t="inlineStr"/>
+      <c r="BK59" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL59" s="10" t="n"/>
       <c r="BM59" s="10" t="n"/>
       <c r="BN59" s="10" t="n"/>
@@ -14498,136 +14534,74 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
-    <row r="60" ht="112" customHeight="1">
-      <c r="A60" s="44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B60" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-043</t>
-        </is>
-      </c>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>共通エラーハンドリング（Common Error Handling）</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="46" t="inlineStr">
-        <is>
-          <t>削除ボタンの活性／非活性制御</t>
-        </is>
-      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・`deleted_at` が NULL の行と NOT NULL の行が各1件以上存在</t>
-        </is>
-      </c>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="10" t="n"/>
       <c r="N60" s="10" t="n"/>
       <c r="O60" s="10" t="n"/>
-      <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>「アップロードされたファイルリスト」で各行の「削除」ボタンの状態を確認</t>
-          </r>
-        </is>
-      </c>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
       <c r="R60" s="10" t="n"/>
       <c r="S60" s="10" t="n"/>
       <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="11" t="n"/>
-      <c r="X60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・`deleted_at` が NULL の行は「削除」ボタンが活性状態で表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`deleted_at` が NOT NULL の行は「削除」ボタンが非活性状態で表示されること</t>
-          </r>
-        </is>
-      </c>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="10" t="n"/>
       <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="11" t="n"/>
-      <c r="AE60" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF60" s="11" t="n"/>
-      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
       <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="11" t="n"/>
-      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
       <c r="AK60" s="10" t="n"/>
-      <c r="AL60" s="11" t="n"/>
-      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AL60" s="10" t="n"/>
+      <c r="AM60" s="10" t="n"/>
       <c r="AN60" s="10" t="n"/>
-      <c r="AO60" s="11" t="n"/>
-      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AO60" s="10" t="n"/>
+      <c r="AP60" s="10" t="n"/>
       <c r="AQ60" s="10" t="n"/>
-      <c r="AR60" s="11" t="n"/>
-      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AR60" s="10" t="n"/>
+      <c r="AS60" s="10" t="n"/>
       <c r="AT60" s="10" t="n"/>
-      <c r="AU60" s="11" t="n"/>
-      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AU60" s="10" t="n"/>
+      <c r="AV60" s="10" t="n"/>
       <c r="AW60" s="10" t="n"/>
-      <c r="AX60" s="11" t="n"/>
-      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AX60" s="10" t="n"/>
+      <c r="AY60" s="10" t="n"/>
       <c r="AZ60" s="10" t="n"/>
-      <c r="BA60" s="11" t="n"/>
-      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BA60" s="10" t="n"/>
+      <c r="BB60" s="10" t="n"/>
       <c r="BC60" s="10" t="n"/>
-      <c r="BD60" s="11" t="n"/>
-      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BD60" s="10" t="n"/>
+      <c r="BE60" s="10" t="n"/>
       <c r="BF60" s="10" t="n"/>
-      <c r="BG60" s="11" t="n"/>
-      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BG60" s="10" t="n"/>
+      <c r="BH60" s="10" t="n"/>
       <c r="BI60" s="10" t="n"/>
-      <c r="BJ60" s="11" t="n"/>
-      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BJ60" s="10" t="n"/>
+      <c r="BK60" s="10" t="n"/>
       <c r="BL60" s="10" t="n"/>
       <c r="BM60" s="10" t="n"/>
       <c r="BN60" s="10" t="n"/>
@@ -14635,20 +14609,20 @@
       <c r="BP60" s="10" t="n"/>
       <c r="BQ60" s="11" t="n"/>
     </row>
-    <row r="61" ht="192" customHeight="1">
+    <row r="61" ht="144" customHeight="1">
       <c r="A61" s="44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-044</t>
+          <t>ACSMS-TC-023-043</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="46" t="inlineStr">
         <is>
-          <t>削除確認ダイアログのキャンセル</t>
+          <t>セッション失効時の401ハンドリング</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -14659,7 +14633,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・ログイン済 + MFA認証済
-・削除対象ファイル（`deleted_at` が NULL）が存在</t>
+・セッションを強制的に失効させた状態</t>
         </is>
       </c>
       <c r="K61" s="10" t="n"/>
@@ -14684,41 +14658,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">対象行の「削除」ボタンを押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">確認ダイアログ（ACSMS-MSG-023-009）で「キャンセル」を押下
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DB確認: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+            <t>セッション失効後、画面上の任意の操作（ファイル一覧の再取得など）を実行</t>
           </r>
         </is>
       </c>
@@ -14744,41 +14684,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・確認ダイアログが表示されること（メッセージ `このファイルを削除しますか？`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・現在の画面が維持されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・データが削除されないこと（`deleted_at IS NULL` のまま）</t>
+            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・セッション切れ時、ログイン画面（`/login?redirect=...`）へ遷移すること</t>
           </r>
         </is>
       </c>
@@ -14832,20 +14746,20 @@
       <c r="BP61" s="10" t="n"/>
       <c r="BQ61" s="11" t="n"/>
     </row>
-    <row r="62" ht="192" customHeight="1">
+    <row r="62" ht="96" customHeight="1">
       <c r="A62" s="44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-045</t>
+          <t>ACSMS-TC-023-044</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="46" t="inlineStr">
         <is>
-          <t>削除済ファイルのダウンロード（NOT_FOUND）</t>
+          <t>不正なリクエストパラメータ送信（BAD_REQUEST）</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -14855,8 +14769,7 @@
       <c r="J62" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・論理削除済（`deleted_at IS NOT NULL`）のファイル（`file_upload_id = 301`）が存在</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K62" s="10" t="n"/>
@@ -14881,7 +14794,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsで GET `/api/v1/file-upload/301/download` を直接送信</t>
+            <t>DevToolsで GET `/api/v1/file-upload?status=abc&amp;page=-1` のように不正なクエリパラメータを送信</t>
           </r>
         </is>
       </c>
@@ -14907,24 +14820,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード404が返却されること（`error_code: NOT_FOUND`、メッセージ `指定されたファイルが見つかりません。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・論理削除済みのレコードはダウンロード対象外であること（`deleted_at IS NULL` 条件で除外されること）</t>
+            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。`）</t>
           </r>
         </is>
       </c>
@@ -14970,12 +14866,7 @@
       <c r="BH62" s="45" t="inlineStr"/>
       <c r="BI62" s="10" t="n"/>
       <c r="BJ62" s="11" t="n"/>
-      <c r="BK62" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK62" s="46" t="inlineStr"/>
       <c r="BL62" s="10" t="n"/>
       <c r="BM62" s="10" t="n"/>
       <c r="BN62" s="10" t="n"/>
@@ -14983,74 +14874,135 @@
       <c r="BP62" s="10" t="n"/>
       <c r="BQ62" s="11" t="n"/>
     </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
-        <is>
-          <t>共通エラーハンドリング（Common Error Handling）</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n"/>
+    <row r="63" ht="208" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-045</t>
+        </is>
+      </c>
       <c r="C63" s="10" t="n"/>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>バリデーションエラー（errors配列形状）</t>
+        </is>
+      </c>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・ログイン済 + MFA認証済</t>
+        </is>
+      </c>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevToolsで対象Ja未指定（`ja_ids` 空）のまま POST `/api/v1/file-upload` を送信</t>
+          </r>
+        </is>
+      </c>
       <c r="R63" s="10" t="n"/>
       <c r="S63" s="10" t="n"/>
       <c r="T63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・レスポンスに `errors` 配列が含まれ、`{ field, message }` の形状であること（例: `field: "ja_ids"`、`message: "対象JAを1つ以上選択してください。"`）</t>
+          </r>
+        </is>
+      </c>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="10" t="n"/>
       <c r="AC63" s="10" t="n"/>
-      <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
-      <c r="AG63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
       <c r="AH63" s="10" t="n"/>
-      <c r="AI63" s="10" t="n"/>
-      <c r="AJ63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
       <c r="AK63" s="10" t="n"/>
-      <c r="AL63" s="10" t="n"/>
-      <c r="AM63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
       <c r="AN63" s="10" t="n"/>
-      <c r="AO63" s="10" t="n"/>
-      <c r="AP63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
       <c r="AQ63" s="10" t="n"/>
-      <c r="AR63" s="10" t="n"/>
-      <c r="AS63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
       <c r="AT63" s="10" t="n"/>
-      <c r="AU63" s="10" t="n"/>
-      <c r="AV63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
       <c r="AW63" s="10" t="n"/>
-      <c r="AX63" s="10" t="n"/>
-      <c r="AY63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
       <c r="AZ63" s="10" t="n"/>
-      <c r="BA63" s="10" t="n"/>
-      <c r="BB63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
       <c r="BC63" s="10" t="n"/>
-      <c r="BD63" s="10" t="n"/>
-      <c r="BE63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
       <c r="BF63" s="10" t="n"/>
-      <c r="BG63" s="10" t="n"/>
-      <c r="BH63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
       <c r="BI63" s="10" t="n"/>
-      <c r="BJ63" s="10" t="n"/>
-      <c r="BK63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr"/>
       <c r="BL63" s="10" t="n"/>
       <c r="BM63" s="10" t="n"/>
       <c r="BN63" s="10" t="n"/>
@@ -15058,7 +15010,7 @@
       <c r="BP63" s="10" t="n"/>
       <c r="BQ63" s="11" t="n"/>
     </row>
-    <row r="64" ht="144" customHeight="1">
+    <row r="64" ht="112" customHeight="1">
       <c r="A64" s="44" t="n">
         <v>46</v>
       </c>
@@ -15071,7 +15023,7 @@
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="46" t="inlineStr">
         <is>
-          <t>セッション失効時の401ハンドリング</t>
+          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
         </is>
       </c>
       <c r="F64" s="10" t="n"/>
@@ -15081,8 +15033,7 @@
       <c r="J64" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・セッションを強制的に失効させた状態</t>
+・ログイン済 + MFA認証済</t>
         </is>
       </c>
       <c r="K64" s="10" t="n"/>
@@ -15107,7 +15058,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>セッション失効後、画面上の任意の操作（ファイル一覧の再取得など）を実行</t>
+            <t>短時間に上限を超える回数のリクエストを連続送信する</t>
           </r>
         </is>
       </c>
@@ -15133,15 +15084,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・HTTPステータスコード401が返却されること（`error_code: UNAUTHORIZED`、メッセージ `セッションが切れました。再度ログインしてください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・セッション切れ時、ログイン画面（`/login?redirect=...`）へ遷移すること</t>
+            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
           </r>
         </is>
       </c>
@@ -15195,7 +15138,7 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
-    <row r="65" ht="96" customHeight="1">
+    <row r="65" ht="304" customHeight="1">
       <c r="A65" s="44" t="n">
         <v>47</v>
       </c>
@@ -15208,7 +15151,7 @@
       <c r="D65" s="11" t="n"/>
       <c r="E65" s="46" t="inlineStr">
         <is>
-          <t>不正なリクエストパラメータ送信（BAD_REQUEST）</t>
+          <t>サーバーエラー（INTERNAL_SERVER_ERROR）</t>
         </is>
       </c>
       <c r="F65" s="10" t="n"/>
@@ -15218,7 +15161,8 @@
       <c r="J65" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
+・ログイン済 + MFA認証済
+・ストレージ書き込み失敗を模擬できる状態</t>
         </is>
       </c>
       <c r="K65" s="10" t="n"/>
@@ -15243,7 +15187,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsで GET `/api/v1/file-upload?status=abc&amp;page=-1` のように不正なクエリパラメータを送信</t>
+            <t xml:space="preserve">ストレージ書き込み失敗を模擬した状態でアップロードを実行
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（実行前後で件数比較）</t>
           </r>
         </is>
       </c>
@@ -15269,7 +15230,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード400が返却されること（`error_code: BAD_REQUEST`、メッセージ `リクエストパラメータが不正です。`）</t>
+            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・画面にアップロード失敗メッセージ `アップロードに失敗しました。しばらくしてから再度お試しください。`（ACSMS-MSG-023-005）が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・トランザクションがロールバックされ、`t_file_upload` に新規データが登録されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・既に保存された物理ファイルが補償削除されること</t>
           </r>
         </is>
       </c>
@@ -15323,7 +15317,7 @@
       <c r="BP65" s="10" t="n"/>
       <c r="BQ65" s="11" t="n"/>
     </row>
-    <row r="66" ht="208" customHeight="1">
+    <row r="66" ht="96" customHeight="1">
       <c r="A66" s="44" t="n">
         <v>48</v>
       </c>
@@ -15336,7 +15330,7 @@
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="46" t="inlineStr">
         <is>
-          <t>バリデーションエラー（errors配列形状）</t>
+          <t>削除済リソースの取得（NOT_FOUND）</t>
         </is>
       </c>
       <c r="F66" s="10" t="n"/>
@@ -15346,7 +15340,8 @@
       <c r="J66" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
+・ログイン済 + MFA認証済
+・論理削除済のファイル（`file_upload_id = 301`）が存在</t>
         </is>
       </c>
       <c r="K66" s="10" t="n"/>
@@ -15371,7 +15366,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsで対象Ja未指定（`ja_ids` 空）のまま POST `/api/v1/file-upload` を送信</t>
+            <t>DevToolsで DELETE `/api/v1/file-upload/301` を直接送信（既に削除済のレコード）</t>
           </r>
         </is>
       </c>
@@ -15397,15 +15392,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、メッセージ `入力値が不正です。詳細はerrorsフィールドを確認してください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・レスポンスに `errors` 配列が含まれ、`{ field, message }` の形状であること（例: `field: "ja_ids"`、`message: "対象JAを1つ以上選択してください。"`）</t>
+            <t>HTTPステータスコード404が返却されること（`error_code: NOT_FOUND`、メッセージ `指定されたファイルが見つかりません。`）</t>
           </r>
         </is>
       </c>
@@ -15472,7 +15459,7 @@
       <c r="D67" s="11" t="n"/>
       <c r="E67" s="46" t="inlineStr">
         <is>
-          <t>レート制限超過（TOO_MANY_REQUESTS）</t>
+          <t>ネットワーク切断時のハンドリング</t>
         </is>
       </c>
       <c r="F67" s="10" t="n"/>
@@ -15507,7 +15494,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>短時間に上限を超える回数のリクエストを連続送信する</t>
+            <t>DevToolsのNetworkタブでネットワーク切断を模擬した状態で「アップロード実行」を押下</t>
           </r>
         </is>
       </c>
@@ -15533,7 +15520,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード429が返却されること（`error_code: TOO_MANY_REQUESTS`、メッセージ `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`）</t>
+            <t xml:space="preserve">・フロントエンド側でネットワークエラーのトーストが表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・想定外エラーが発生しないこと（画面が異常終了しないこと）</t>
           </r>
         </is>
       </c>
@@ -15587,7 +15582,7 @@
       <c r="BP67" s="10" t="n"/>
       <c r="BQ67" s="11" t="n"/>
     </row>
-    <row r="68" ht="304" customHeight="1">
+    <row r="68" ht="450" customHeight="1">
       <c r="A68" s="44" t="n">
         <v>50</v>
       </c>
@@ -15600,7 +15595,7 @@
       <c r="D68" s="11" t="n"/>
       <c r="E68" s="46" t="inlineStr">
         <is>
-          <t>サーバーエラー（INTERNAL_SERVER_ERROR）</t>
+          <t>アップロードしたファイルがダウンロード画面(SCR-022)から取得できる</t>
         </is>
       </c>
       <c r="F68" s="10" t="n"/>
@@ -15609,9 +15604,9 @@
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・ストレージ書き込み失敗を模擬できる状態</t>
+          <t>・role: NICHINO_STAFF（`file.upload` 権限あり）でログイン
+・JA「JA北海道」（ja_id=100）が存在し、そのJAに JA_HONTEN(role 4) のアカウント（`file.download` 権限あり）が存在
+・別JA「JA東京」（ja_id=200）にも JA_HONTEN のアカウントが存在（スコープ確認用）</t>
         </is>
       </c>
       <c r="K68" s="10" t="n"/>
@@ -15636,7 +15631,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ストレージ書き込み失敗を模擬した状態でアップロードを実行
+            <t xml:space="preserve">ファイルアップロード画面で対象JAに「JA北海道」のみを選択し、削除予定日を翌月1日、ファイル `検査結果.xlsx` を1件アップロードする
 </t>
           </r>
           <r>
@@ -15653,7 +15648,58 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DB確認: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（実行前後で件数比較）</t>
+            <t xml:space="preserve">DBで `t_file_upload` と `t_file_download` の該当行を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面を開いてファイル名で検索し、ファイル名リンクを押下する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「JA東京」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面で同じファイル名を検索する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>アップロード者（NICHINO_STAFF）でファイルアップロード画面に戻り、当該行の「削除」を実行したうえで、再度ファイルダウンロード画面を開く</t>
           </r>
         </is>
       </c>
@@ -15679,15 +15725,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード500が返却されること（`error_code: INTERNAL_SERVER_ERROR`、メッセージ `システムエラーが発生しました。しばらくしてから再度お試しください。`）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・画面にアップロード失敗メッセージ `アップロードに失敗しました。しばらくしてから再度お試しください。`（ACSMS-MSG-023-005）が表示されること
+            <t xml:space="preserve">HTTP 202 が返り、ACSMS-MSG-023-006 が表示されること
 </t>
           </r>
           <r>
@@ -15704,15 +15742,91 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・トランザクションがロールバックされ、`t_file_upload` に新規データが登録されないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・既に保存された物理ファイルが補償削除されること</t>
+            <t xml:space="preserve">`t_file_upload` 1件に対して `t_file_download` も1件登録されており、`ja_id`=100、`download_type`=2（その他）、`nichino_download_allowed_flg`=TRUE、`record_count`=0、`file_path` と `scheduled_delete_date` が `t_file_upload` と同値であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">一覧に当該ファイルが表示され、ダウンロードが成功して中身が投入したファイルと一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">0件であること（DataScope により他JAのファイルは見えない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ダウンロード画面の一覧から当該ファイルが消えている（`t_file_download.deleted_at` も設定されている）こと。実体(S3)が消えているのに一覧へ残る状態にならないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ダウンロード画面は `t_file_download` のみを一覧・取得対象とするため、アップロード時にペア行を登録しないと JA 側（role 3/4/5）はファイルを一切取得できない（顧客要件2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`nichino_download_allowed_flg`=TRUE 固定は、日農・中央会が自組織で上げたファイルを取り直せないと運用が回らないため。帳票出力（SCR-021/026/028/029）は画面ごとの固定／選択で、本画面限定の既定
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ペア行の突合キーは `file_path`。S3キーに UUID を含むため一意で、FK列の追加（マイグレーション＋既存帳票行への影響）を伴わずにペアを解決できる</t>
           </r>
         </is>
       </c>
@@ -15724,7 +15838,7 @@
       <c r="AD68" s="11" t="n"/>
       <c r="AE68" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF68" s="11" t="n"/>
@@ -15758,7 +15872,12 @@
       <c r="BH68" s="45" t="inlineStr"/>
       <c r="BI68" s="10" t="n"/>
       <c r="BJ68" s="11" t="n"/>
-      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BK68" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL68" s="10" t="n"/>
       <c r="BM68" s="10" t="n"/>
       <c r="BN68" s="10" t="n"/>
@@ -15766,7 +15885,7 @@
       <c r="BP68" s="10" t="n"/>
       <c r="BQ68" s="11" t="n"/>
     </row>
-    <row r="69" ht="96" customHeight="1">
+    <row r="69" ht="450" customHeight="1">
       <c r="A69" s="44" t="n">
         <v>51</v>
       </c>
@@ -15779,7 +15898,7 @@
       <c r="D69" s="11" t="n"/>
       <c r="E69" s="46" t="inlineStr">
         <is>
-          <t>削除済リソースの取得（NOT_FOUND）</t>
+          <t>通知メールのダウンロードリンク</t>
         </is>
       </c>
       <c r="F69" s="10" t="n"/>
@@ -15788,9 +15907,10 @@
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済
-・論理削除済のファイル（`file_upload_id = 301`）が存在</t>
+          <t>・role: NICHINO_STAFF（`file.upload` 権限あり）でログイン
+・JA「JA北海道」（ja_id=100）に受信可能なメールアドレスを持つアカウントが1件以上存在
+・`FRONTEND_URL` が設定済み（例: `https://acsms.example.com`）
+・通知ワーカー（file-upload-notification）が稼働中</t>
         </is>
       </c>
       <c r="K69" s="10" t="n"/>
@@ -15815,7 +15935,75 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevToolsで DELETE `/api/v1/file-upload/301` を直接送信（既に削除済のレコード）</t>
+            <t xml:space="preserve">「JA北海道」向けに `増減通知 2026年04月.pdf` をアップロードし、通知ステータスが「完了」になるまで待つ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">受信した通知メールの本文を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">未ログイン状態のブラウザで本文中のリンクを開く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>`FRONTEND_URL` を未設定にした環境で同じ手順を実行し、本文を確認する</t>
           </r>
         </is>
       </c>
@@ -15841,7 +16029,108 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>HTTPステータスコード404が返却されること（`error_code: NOT_FOUND`、メッセージ `指定されたファイルが見つかりません。`）</t>
+            <t xml:space="preserve">`notification_status` が 3:完了 になること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文に「下記のリンクからダウンロードしてください。」の案内と、`https://acsms.example.com/file-download?file_name=%E5%A2%97%E6%B8%9B%E9%80%9A%E7%9F%A5%202026%E5%B9%B404%E6%9C%88.pdf` の形式のURLが記載されていること。ファイル名がURLエンコードされており、スペースでリンクが途切れないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログイン画面へ遷移し、URLに `redirect` パラメータが付いていること（401のJSONが表示されないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ファイルダウンロード画面へ遷移し、ファイル名検索欄に `増減通知 2026年04月.pdf` が入った状態で、該当ファイルのみが一覧表示されること。続けて「検索クリア」を押すと絞り込みが解除されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">リンクの行（案内文とURL）が本文から省略され、他の項目（JA名・ファイル名・アップロード日時・アップロード者・送信専用フッター）は従来どおり出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・2026-07 時点は「環境依存の絶対URLは本文に含めない」方針だったが、2026-08 に「リンクを載せる」へ変更された
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・API の直リンク（`/api/v1/file-download/{id}/download`）にしないのは、未ログインだと 401 の JSON が返るだけでログイン導線が無いため。画面URLならルーターガードがログインへ回し、認証後に元のURLへ戻す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`FRONTEND_URL` 未設定時にリンク行ごと落とすのは、`undefined/file-download` のような壊れたリンクを本文に出さないため</t>
           </r>
         </is>
       </c>
@@ -15853,7 +16142,7 @@
       <c r="AD69" s="11" t="n"/>
       <c r="AE69" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF69" s="11" t="n"/>
@@ -15887,7 +16176,12 @@
       <c r="BH69" s="45" t="inlineStr"/>
       <c r="BI69" s="10" t="n"/>
       <c r="BJ69" s="11" t="n"/>
-      <c r="BK69" s="46" t="inlineStr"/>
+      <c r="BK69" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL69" s="10" t="n"/>
       <c r="BM69" s="10" t="n"/>
       <c r="BN69" s="10" t="n"/>
@@ -15895,157 +16189,22 @@
       <c r="BP69" s="10" t="n"/>
       <c r="BQ69" s="11" t="n"/>
     </row>
-    <row r="70" ht="112" customHeight="1">
-      <c r="A70" s="44" t="n">
-        <v>52</v>
-      </c>
-      <c r="B70" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-052</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="46" t="inlineStr">
-        <is>
-          <t>ネットワーク切断時のハンドリング</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・ログイン済 + MFA認証済</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="11" t="n"/>
-      <c r="Q70" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DevToolsのNetworkタブでネットワーク切断を模擬した状態で「アップロード実行」を押下</t>
-          </r>
-        </is>
-      </c>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="11" t="n"/>
-      <c r="X70" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・フロントエンド側でネットワークエラーのトーストが表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・想定外エラーが発生しないこと（画面が異常終了しないこと）</t>
-          </r>
-        </is>
-      </c>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="11" t="n"/>
-      <c r="AE70" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF70" s="11" t="n"/>
-      <c r="AG70" s="45" t="inlineStr"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="11" t="n"/>
-      <c r="AJ70" s="45" t="inlineStr"/>
-      <c r="AK70" s="10" t="n"/>
-      <c r="AL70" s="11" t="n"/>
-      <c r="AM70" s="45" t="inlineStr"/>
-      <c r="AN70" s="10" t="n"/>
-      <c r="AO70" s="11" t="n"/>
-      <c r="AP70" s="45" t="inlineStr"/>
-      <c r="AQ70" s="10" t="n"/>
-      <c r="AR70" s="11" t="n"/>
-      <c r="AS70" s="45" t="inlineStr"/>
-      <c r="AT70" s="10" t="n"/>
-      <c r="AU70" s="11" t="n"/>
-      <c r="AV70" s="45" t="inlineStr"/>
-      <c r="AW70" s="10" t="n"/>
-      <c r="AX70" s="11" t="n"/>
-      <c r="AY70" s="45" t="inlineStr"/>
-      <c r="AZ70" s="10" t="n"/>
-      <c r="BA70" s="11" t="n"/>
-      <c r="BB70" s="45" t="inlineStr"/>
-      <c r="BC70" s="10" t="n"/>
-      <c r="BD70" s="11" t="n"/>
-      <c r="BE70" s="45" t="inlineStr"/>
-      <c r="BF70" s="10" t="n"/>
-      <c r="BG70" s="11" t="n"/>
-      <c r="BH70" s="45" t="inlineStr"/>
-      <c r="BI70" s="10" t="n"/>
-      <c r="BJ70" s="11" t="n"/>
-      <c r="BK70" s="46" t="inlineStr"/>
-      <c r="BL70" s="10" t="n"/>
-      <c r="BM70" s="10" t="n"/>
-      <c r="BN70" s="10" t="n"/>
-      <c r="BO70" s="10" t="n"/>
-      <c r="BP70" s="10" t="n"/>
-      <c r="BQ70" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="957">
+  <mergeCells count="940">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="Q27:W27"/>
+    <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
+    <mergeCell ref="BB68:BD68"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="E52:I52"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A45:BQ45"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AS61:AU61"/>
@@ -16054,14 +16213,14 @@
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
+    <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AP45:AR45"/>
     <mergeCell ref="J64:P64"/>
-    <mergeCell ref="A46:BQ46"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
+    <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
@@ -16070,7 +16229,6 @@
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
-    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
@@ -16086,8 +16244,8 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
-    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
+    <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
@@ -16102,42 +16260,45 @@
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="AG45:AI45"/>
     <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="AJ33:AL33"/>
+    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
-    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
-    <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
     <mergeCell ref="BK37:BQ37"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
+    <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK66:BQ66"/>
+    <mergeCell ref="A32:BQ32"/>
     <mergeCell ref="BK53:BQ53"/>
-    <mergeCell ref="BH60:BJ60"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
-    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AP68:AR68"/>
     <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
+    <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP67:AR67"/>
@@ -16148,15 +16309,14 @@
     <mergeCell ref="BE41:BG41"/>
     <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
-    <mergeCell ref="BH55:BJ55"/>
+    <mergeCell ref="Q46:W46"/>
     <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
+    <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
@@ -16169,7 +16329,7 @@
     <mergeCell ref="AY44:BA44"/>
     <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="BH44:BJ44"/>
-    <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="Q56:W56"/>
     <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
@@ -16182,24 +16342,25 @@
     <mergeCell ref="BH24:BJ24"/>
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="BE34:BG34"/>
+    <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
     <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AG55:AI55"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
-    <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BE29:BG29"/>
-    <mergeCell ref="AY32:BA32"/>
+    <mergeCell ref="BK28:BQ28"/>
+    <mergeCell ref="BB33:BD33"/>
+    <mergeCell ref="AG46:AI46"/>
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
@@ -16213,6 +16374,7 @@
     <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
     <mergeCell ref="BK67:BQ67"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -16220,18 +16382,19 @@
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="AJ69:AL69"/>
     <mergeCell ref="BK69:BQ69"/>
-    <mergeCell ref="AM70:AO70"/>
     <mergeCell ref="BE43:BG43"/>
+    <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
-    <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="AG66:AI66"/>
+    <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="AY60:BA60"/>
     <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
@@ -16240,37 +16403,33 @@
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="AY45:BA45"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="E36:I36"/>
-    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
-    <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AV65:AX65"/>
-    <mergeCell ref="BH45:BJ45"/>
+    <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="BK18:BQ18"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A19:BQ19"/>
     <mergeCell ref="AY22:BA22"/>
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
+    <mergeCell ref="X20:AD20"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
-    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="BE44:BG44"/>
-    <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
@@ -16285,18 +16444,22 @@
     <mergeCell ref="AV34:AX34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
+    <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
+    <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
     <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
@@ -16311,13 +16474,10 @@
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
-    <mergeCell ref="A63:BQ63"/>
     <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
-    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
-    <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
@@ -16326,25 +16486,24 @@
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="E42:I42"/>
     <mergeCell ref="Q65:W65"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
-    <mergeCell ref="BK19:BQ19"/>
+    <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
-    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AS28:AU28"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
-    <mergeCell ref="BE70:BG70"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -16353,24 +16512,20 @@
     <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
-    <mergeCell ref="AJ60:AL60"/>
-    <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="AG51:AI51"/>
+    <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
-    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="AS54:AU54"/>
-    <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
@@ -16378,16 +16533,16 @@
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="AG65:AI65"/>
-    <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="AV52:AX52"/>
-    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
@@ -16402,10 +16557,10 @@
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
@@ -16414,21 +16569,16 @@
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="AY69:BA69"/>
-    <mergeCell ref="E60:I60"/>
     <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
-    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="BK27:BQ27"/>
+    <mergeCell ref="Q33:W33"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="AV45:AX45"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="AV32:AX32"/>
     <mergeCell ref="AV26:AX26"/>
-    <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
@@ -16436,18 +16586,13 @@
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="BB19:BD19"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
-    <mergeCell ref="J70:P70"/>
-    <mergeCell ref="A28:BQ28"/>
     <mergeCell ref="AS44:AU44"/>
-    <mergeCell ref="AV27:AX27"/>
-    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="X64:AD64"/>
     <mergeCell ref="BH18:BJ18"/>
-    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
@@ -16456,51 +16601,51 @@
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
+    <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
+    <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
-    <mergeCell ref="BK55:BQ55"/>
-    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
+    <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
     <mergeCell ref="AS57:AU57"/>
-    <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A56:BQ56"/>
+    <mergeCell ref="A27:BQ27"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP56:AR56"/>
+    <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
-    <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E66:I66"/>
     <mergeCell ref="E53:I53"/>
-    <mergeCell ref="AE70:AF70"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="E68:I68"/>
@@ -16508,8 +16653,6 @@
     <mergeCell ref="AM44:AO44"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
-    <mergeCell ref="E55:I55"/>
-    <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
@@ -16525,14 +16668,9 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
-    <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J58:P58"/>
-    <mergeCell ref="AS32:AU32"/>
-    <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="BH19:BJ19"/>
-    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
@@ -16541,38 +16679,35 @@
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
-    <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="Q29:W29"/>
     <mergeCell ref="AG35:AI35"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
-    <mergeCell ref="B62:D62"/>
     <mergeCell ref="AV66:AX66"/>
-    <mergeCell ref="X19:AD19"/>
-    <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
+    <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
     <mergeCell ref="BE49:BG49"/>
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
+    <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
-    <mergeCell ref="AS60:AU60"/>
     <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
@@ -16584,20 +16719,21 @@
     <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="AM67:AO67"/>
-    <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
+    <mergeCell ref="J46:P46"/>
+    <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AP65:AR65"/>
+    <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
@@ -16617,23 +16753,24 @@
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="BH27:BJ27"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
+    <mergeCell ref="BH20:BJ20"/>
     <mergeCell ref="AG54:AI54"/>
-    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
     <mergeCell ref="AM38:AO38"/>
+    <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
+    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
     <mergeCell ref="BK52:BQ52"/>
+    <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="AJ39:AL39"/>
@@ -16653,13 +16790,10 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
-    <mergeCell ref="Q45:W45"/>
     <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
-    <mergeCell ref="Q32:W32"/>
     <mergeCell ref="AY35:BA35"/>
     <mergeCell ref="X22:AD22"/>
     <mergeCell ref="BH38:BJ38"/>
@@ -16667,11 +16801,11 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="AS66:AU66"/>
-    <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="J67:P67"/>
     <mergeCell ref="BK21:BQ21"/>
+    <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="AV64:AX64"/>
@@ -16679,39 +16813,40 @@
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AS68:AU68"/>
-    <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
     <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="A20:BQ20"/>
-    <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
     <mergeCell ref="E37:I37"/>
+    <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
+    <mergeCell ref="AY56:BA56"/>
     <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
+    <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
-    <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="X35:AD35"/>
     <mergeCell ref="AE10:AF11"/>
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -16721,46 +16856,40 @@
     <mergeCell ref="BB44:BD44"/>
     <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AV10:BJ10"/>
-    <mergeCell ref="BE27:BG27"/>
+    <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
     <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
-    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="BB70:BD70"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="AG58:AI58"/>
-    <mergeCell ref="BB32:BD32"/>
-    <mergeCell ref="Q55:W55"/>
-    <mergeCell ref="A33:BQ33"/>
     <mergeCell ref="AY36:BA36"/>
-    <mergeCell ref="E27:I27"/>
     <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X34:AD34"/>
+    <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="AE69:AF69"/>
-    <mergeCell ref="BB47:BD47"/>
-    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
-    <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="AS69:AU69"/>
+    <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
     <mergeCell ref="AP35:AR35"/>
     <mergeCell ref="BH31:BJ31"/>
@@ -16768,19 +16897,23 @@
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="AJ66:AL66"/>
-    <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="BK20:BQ20"/>
+    <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AJ68:AL68"/>
-    <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
     <mergeCell ref="Q53:W53"/>
+    <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
@@ -16790,32 +16923,34 @@
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
     <mergeCell ref="E15:I15"/>
+    <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
     <mergeCell ref="AS24:AU24"/>
     <mergeCell ref="AS18:AU18"/>
-    <mergeCell ref="AM27:AO27"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
-    <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AY33:BA33"/>
     <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="J20:P20"/>
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
-    <mergeCell ref="BB55:BD55"/>
+    <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
@@ -16833,24 +16968,28 @@
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="BB25:BD25"/>
     <mergeCell ref="AP49:AR49"/>
+    <mergeCell ref="E28:I28"/>
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="BE67:BG67"/>
+    <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
     <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A55:BQ55"/>
     <mergeCell ref="E59:I59"/>
+    <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
@@ -16869,29 +17008,31 @@
     <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB68:BD68"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="Q69:W69"/>
-    <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
-    <mergeCell ref="BK29:BQ29"/>
+    <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="AE25:AF25"/>
+    <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
     <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
-    <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="A60:BQ60"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
@@ -16900,18 +17041,22 @@
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
+    <mergeCell ref="AY20:BA20"/>
+    <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J28:P28"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
     <mergeCell ref="AG67:AI67"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -16920,13 +17065,12 @@
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
-    <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
-    <mergeCell ref="Q19:W19"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AS38:AU38"/>
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
@@ -16936,17 +17080,17 @@
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
-    <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AM62:AO62"/>
+    <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
-    <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="E62:I62"/>
+    <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
@@ -16958,20 +17102,16 @@
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
-    <mergeCell ref="AP32:AR32"/>
-    <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="X66:AD66"/>
-    <mergeCell ref="BE19:BG19"/>
-    <mergeCell ref="BK32:BQ32"/>
+    <mergeCell ref="AM33:AO33"/>
     <mergeCell ref="BK26:BQ26"/>
+    <mergeCell ref="AE28:AF28"/>
     <mergeCell ref="AP47:AR47"/>
     <mergeCell ref="BH30:BJ30"/>
     <mergeCell ref="AV31:AX31"/>
@@ -16983,22 +17123,23 @@
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
+    <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
-    <mergeCell ref="BE60:BG60"/>
+    <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE19 AE21:AE27 AE29:AE32 AE34:AE45 AE47:AE55 AE57:AE62 AE64:AE70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE31 AE33:AE44 AE46:AE54 AE56:AE59 AE61:AE69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG19 AG21:AG27 AG29:AG32 AG34:AG45 AG47:AG55 AG57:AG62 AG64:AG70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG31 AG33:AG44 AG46:AG54 AG56:AG59 AG61:AG69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV19 AV21:AV27 AV29:AV32 AV34:AV45 AV47:AV55 AV57:AV62 AV64:AV70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV31 AV33:AV44 AV46:AV54 AV56:AV59 AV61:AV69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1415,26 +1415,86 @@
       <c r="AG3" s="10" t="n"/>
       <c r="AH3" s="11" t="n"/>
     </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：v1.1（2026-07-02）でダウンロード・プレビューのケースを削除したが、顧客要件により 2026/07/27 に機能が**再追加**されていた。カテゴリ8を新設し3件追加（TC-052〜054）＝プレビュー（署名付きURL・範囲外/削除済は404マスク）、単体ダウンロード（`t_file_download` へINSERTしないこと＝旧仕様との差分回帰、`t_log` に DOWNLOAD 証跡）、ZIP一括（1〜50件・重複不可・1件でも範囲外なら全体拒否・ログはZIP全体で1件・レート制限20回/分）。あわせて集計表を実数に合わせた（49→54。既存の050/051 がカテゴリ7配下に紛れて未計上だった）</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6406,7 +6466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ69"/>
+  <dimension ref="A1:BQ73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15582,302 +15642,74 @@
       <c r="BP67" s="10" t="n"/>
       <c r="BQ67" s="11" t="n"/>
     </row>
-    <row r="68" ht="450" customHeight="1">
-      <c r="A68" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="B68" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-050</t>
-        </is>
-      </c>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック — 連携・プレビュー・ダウンロード（Function — Link / Preview / Download）</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="46" t="inlineStr">
-        <is>
-          <t>アップロードしたファイルがダウンロード画面(SCR-022)から取得できる</t>
-        </is>
-      </c>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="11" t="n"/>
-      <c r="J68" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_STAFF（`file.upload` 権限あり）でログイン
-・JA「JA北海道」（ja_id=100）が存在し、そのJAに JA_HONTEN(role 4) のアカウント（`file.download` 権限あり）が存在
-・別JA「JA東京」（ja_id=200）にも JA_HONTEN のアカウントが存在（スコープ確認用）</t>
-        </is>
-      </c>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
       <c r="K68" s="10" t="n"/>
       <c r="L68" s="10" t="n"/>
       <c r="M68" s="10" t="n"/>
       <c r="N68" s="10" t="n"/>
       <c r="O68" s="10" t="n"/>
-      <c r="P68" s="11" t="n"/>
-      <c r="Q68" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ファイルアップロード画面で対象JAに「JA北海道」のみを選択し、削除予定日を翌月1日、ファイル `検査結果.xlsx` を1件アップロードする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">DBで `t_file_upload` と `t_file_download` の該当行を確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面を開いてファイル名で検索し、ファイル名リンクを押下する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">「JA東京」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面で同じファイル名を検索する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>アップロード者（NICHINO_STAFF）でファイルアップロード画面に戻り、当該行の「削除」を実行したうえで、再度ファイルダウンロード画面を開く</t>
-          </r>
-        </is>
-      </c>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
       <c r="R68" s="10" t="n"/>
       <c r="S68" s="10" t="n"/>
       <c r="T68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
       <c r="V68" s="10" t="n"/>
-      <c r="W68" s="11" t="n"/>
-      <c r="X68" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">HTTP 202 が返り、ACSMS-MSG-023-006 が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">`t_file_upload` 1件に対して `t_file_download` も1件登録されており、`ja_id`=100、`download_type`=2（その他）、`nichino_download_allowed_flg`=TRUE、`record_count`=0、`file_path` と `scheduled_delete_date` が `t_file_upload` と同値であること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">一覧に当該ファイルが表示され、ダウンロードが成功して中身が投入したファイルと一致すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">0件であること（DataScope により他JAのファイルは見えない）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ダウンロード画面の一覧から当該ファイルが消えている（`t_file_download.deleted_at` も設定されている）こと。実体(S3)が消えているのに一覧へ残る状態にならないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・ダウンロード画面は `t_file_download` のみを一覧・取得対象とするため、アップロード時にペア行を登録しないと JA 側（role 3/4/5）はファイルを一切取得できない（顧客要件2026-08）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・`nichino_download_allowed_flg`=TRUE 固定は、日農・中央会が自組織で上げたファイルを取り直せないと運用が回らないため。帳票出力（SCR-021/026/028/029）は画面ごとの固定／選択で、本画面限定の既定
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・ペア行の突合キーは `file_path`。S3キーに UUID を含むため一意で、FK列の追加（マイグレーション＋既存帳票行への影響）を伴わずにペアを解決できる</t>
-          </r>
-        </is>
-      </c>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
       <c r="AB68" s="10" t="n"/>
       <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="11" t="n"/>
-      <c r="AE68" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF68" s="11" t="n"/>
-      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
       <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="11" t="n"/>
-      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
       <c r="AK68" s="10" t="n"/>
-      <c r="AL68" s="11" t="n"/>
-      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AL68" s="10" t="n"/>
+      <c r="AM68" s="10" t="n"/>
       <c r="AN68" s="10" t="n"/>
-      <c r="AO68" s="11" t="n"/>
-      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AO68" s="10" t="n"/>
+      <c r="AP68" s="10" t="n"/>
       <c r="AQ68" s="10" t="n"/>
-      <c r="AR68" s="11" t="n"/>
-      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AR68" s="10" t="n"/>
+      <c r="AS68" s="10" t="n"/>
       <c r="AT68" s="10" t="n"/>
-      <c r="AU68" s="11" t="n"/>
-      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AU68" s="10" t="n"/>
+      <c r="AV68" s="10" t="n"/>
       <c r="AW68" s="10" t="n"/>
-      <c r="AX68" s="11" t="n"/>
-      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AX68" s="10" t="n"/>
+      <c r="AY68" s="10" t="n"/>
       <c r="AZ68" s="10" t="n"/>
-      <c r="BA68" s="11" t="n"/>
-      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BA68" s="10" t="n"/>
+      <c r="BB68" s="10" t="n"/>
       <c r="BC68" s="10" t="n"/>
-      <c r="BD68" s="11" t="n"/>
-      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BD68" s="10" t="n"/>
+      <c r="BE68" s="10" t="n"/>
       <c r="BF68" s="10" t="n"/>
-      <c r="BG68" s="11" t="n"/>
-      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BG68" s="10" t="n"/>
+      <c r="BH68" s="10" t="n"/>
       <c r="BI68" s="10" t="n"/>
-      <c r="BJ68" s="11" t="n"/>
-      <c r="BK68" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ68" s="10" t="n"/>
+      <c r="BK68" s="10" t="n"/>
       <c r="BL68" s="10" t="n"/>
       <c r="BM68" s="10" t="n"/>
       <c r="BN68" s="10" t="n"/>
@@ -15887,18 +15719,18 @@
     </row>
     <row r="69" ht="450" customHeight="1">
       <c r="A69" s="44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B69" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-051</t>
+          <t>ACSMS-TC-023-050</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="11" t="n"/>
       <c r="E69" s="46" t="inlineStr">
         <is>
-          <t>通知メールのダウンロードリンク</t>
+          <t>アップロードしたファイルがダウンロード画面(SCR-022)から取得できる</t>
         </is>
       </c>
       <c r="F69" s="10" t="n"/>
@@ -15908,9 +15740,8 @@
       <c r="J69" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_STAFF（`file.upload` 権限あり）でログイン
-・JA「JA北海道」（ja_id=100）に受信可能なメールアドレスを持つアカウントが1件以上存在
-・`FRONTEND_URL` が設定済み（例: `https://acsms.example.com`）
-・通知ワーカー（file-upload-notification）が稼働中</t>
+・JA「JA北海道」（ja_id=100）が存在し、そのJAに JA_HONTEN(role 4) のアカウント（`file.download` 権限あり）が存在
+・別JA「JA東京」（ja_id=200）にも JA_HONTEN のアカウントが存在（スコープ確認用）</t>
         </is>
       </c>
       <c r="K69" s="10" t="n"/>
@@ -15935,7 +15766,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「JA北海道」向けに `増減通知 2026年04月.pdf` をアップロードし、通知ステータスが「完了」になるまで待つ
+            <t xml:space="preserve">ファイルアップロード画面で対象JAに「JA北海道」のみを選択し、削除予定日を翌月1日、ファイル `検査結果.xlsx` を1件アップロードする
 </t>
           </r>
           <r>
@@ -15952,7 +15783,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">受信した通知メールの本文を確認する
+            <t xml:space="preserve">DBで `t_file_upload` と `t_file_download` の該当行を確認する
 </t>
           </r>
           <r>
@@ -15969,7 +15800,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">未ログイン状態のブラウザで本文中のリンクを開く
+            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面を開いてファイル名で検索し、ファイル名リンクを押下する
 </t>
           </r>
           <r>
@@ -15986,7 +15817,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインする
+            <t xml:space="preserve">「JA東京」の JA_HONTEN アカウントでログインし、ファイルダウンロード画面で同じファイル名を検索する
 </t>
           </r>
           <r>
@@ -16003,7 +15834,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>`FRONTEND_URL` を未設定にした環境で同じ手順を実行し、本文を確認する</t>
+            <t>アップロード者（NICHINO_STAFF）でファイルアップロード画面に戻り、当該行の「削除」を実行したうえで、再度ファイルダウンロード画面を開く</t>
           </r>
         </is>
       </c>
@@ -16029,7 +15860,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`notification_status` が 3:完了 になること
+            <t xml:space="preserve">HTTP 202 が返り、ACSMS-MSG-023-006 が表示されること
 </t>
           </r>
           <r>
@@ -16046,7 +15877,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">本文に「下記のリンクからダウンロードしてください。」の案内と、`https://acsms.example.com/file-download?file_name=%E5%A2%97%E6%B8%9B%E9%80%9A%E7%9F%A5%202026%E5%B9%B404%E6%9C%88.pdf` の形式のURLが記載されていること。ファイル名がURLエンコードされており、スペースでリンクが途切れないこと
+            <t xml:space="preserve">`t_file_upload` 1件に対して `t_file_download` も1件登録されており、`ja_id`=100、`download_type`=2（その他）、`nichino_download_allowed_flg`=TRUE、`record_count`=0、`file_path` と `scheduled_delete_date` が `t_file_upload` と同値であること
 </t>
           </r>
           <r>
@@ -16063,7 +15894,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ログイン画面へ遷移し、URLに `redirect` パラメータが付いていること（401のJSONが表示されないこと）
+            <t xml:space="preserve">一覧に当該ファイルが表示され、ダウンロードが成功して中身が投入したファイルと一致すること
 </t>
           </r>
           <r>
@@ -16080,7 +15911,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ファイルダウンロード画面へ遷移し、ファイル名検索欄に `増減通知 2026年04月.pdf` が入った状態で、該当ファイルのみが一覧表示されること。続けて「検索クリア」を押すと絞り込みが解除されること
+            <t xml:space="preserve">0件であること（DataScope により他JAのファイルは見えない）
 </t>
           </r>
           <r>
@@ -16097,7 +15928,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">リンクの行（案内文とURL）が本文から省略され、他の項目（JA名・ファイル名・アップロード日時・アップロード者・送信専用フッター）は従来どおり出力されること
+            <t xml:space="preserve">ダウンロード画面の一覧から当該ファイルが消えている（`t_file_download.deleted_at` も設定されている）こと。実体(S3)が消えているのに一覧へ残る状態にならないこと
 </t>
           </r>
           <r>
@@ -16114,23 +15945,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・2026-07 時点は「環境依存の絶対URLは本文に含めない」方針だったが、2026-08 に「リンクを載せる」へ変更された
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・API の直リンク（`/api/v1/file-download/{id}/download`）にしないのは、未ログインだと 401 の JSON が返るだけでログイン導線が無いため。画面URLならルーターガードがログインへ回し、認証後に元のURLへ戻す
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`FRONTEND_URL` 未設定時にリンク行ごと落とすのは、`undefined/file-download` のような壊れたリンクを本文に出さないため</t>
+            <t xml:space="preserve">・ダウンロード画面は `t_file_download` のみを一覧・取得対象とするため、アップロード時にペア行を登録しないと JA 側（role 3/4/5）はファイルを一切取得できない（顧客要件2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`nichino_download_allowed_flg`=TRUE 固定は、日農・中央会が自組織で上げたファイルを取り直せないと運用が回らないため。帳票出力（SCR-021/026/028/029）は画面ごとの固定／選択で、本画面限定の既定
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ペア行の突合キーは `file_path`。S3キーに UUID を含むため一意で、FK列の追加（マイグレーション＋既存帳票行への影響）を伴わずにペアを解決できる</t>
           </r>
         </is>
       </c>
@@ -16189,13 +16020,1308 @@
       <c r="BP69" s="10" t="n"/>
       <c r="BQ69" s="11" t="n"/>
     </row>
+    <row r="70" ht="450" customHeight="1">
+      <c r="A70" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-051</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>通知メールのダウンロードリンク</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_STAFF（`file.upload` 権限あり）でログイン
+・JA「JA北海道」（ja_id=100）に受信可能なメールアドレスを持つアカウントが1件以上存在
+・`FRONTEND_URL` が設定済み（例: `https://acsms.example.com`）
+・通知ワーカー（file-upload-notification）が稼働中</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「JA北海道」向けに `増減通知 2026年04月.pdf` をアップロードし、通知ステータスが「完了」になるまで待つ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">受信した通知メールの本文を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">未ログイン状態のブラウザで本文中のリンクを開く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「JA北海道」の JA_HONTEN アカウントでログインする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>`FRONTEND_URL` を未設定にした環境で同じ手順を実行し、本文を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`notification_status` が 3:完了 になること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">本文に「下記のリンクからダウンロードしてください。」の案内と、`https://acsms.example.com/file-download?file_name=%E5%A2%97%E6%B8%9B%E9%80%9A%E7%9F%A5%202026%E5%B9%B404%E6%9C%88.pdf` の形式のURLが記載されていること。ファイル名がURLエンコードされており、スペースでリンクが途切れないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログイン画面へ遷移し、URLに `redirect` パラメータが付いていること（401のJSONが表示されないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ファイルダウンロード画面へ遷移し、ファイル名検索欄に `増減通知 2026年04月.pdf` が入った状態で、該当ファイルのみが一覧表示されること。続けて「検索クリア」を押すと絞り込みが解除されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">リンクの行（案内文とURL）が本文から省略され、他の項目（JA名・ファイル名・アップロード日時・アップロード者・送信専用フッター）は従来どおり出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・2026-07 時点は「環境依存の絶対URLは本文に含めない」方針だったが、2026-08 に「リンクを載せる」へ変更された
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・API の直リンク（`/api/v1/file-download/{id}/download`）にしないのは、未ログインだと 401 の JSON が返るだけでログイン導線が無いため。画面URLならルーターガードがログインへ回し、認証後に元のURLへ戻す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`FRONTEND_URL` 未設定時にリンク行ごと落とすのは、`undefined/file-download` のような壊れたリンクを本文に出さないため</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="45" t="inlineStr"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="45" t="inlineStr"/>
+      <c r="AK70" s="10" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="45" t="inlineStr"/>
+      <c r="AN70" s="10" t="n"/>
+      <c r="AO70" s="11" t="n"/>
+      <c r="AP70" s="45" t="inlineStr"/>
+      <c r="AQ70" s="10" t="n"/>
+      <c r="AR70" s="11" t="n"/>
+      <c r="AS70" s="45" t="inlineStr"/>
+      <c r="AT70" s="10" t="n"/>
+      <c r="AU70" s="11" t="n"/>
+      <c r="AV70" s="45" t="inlineStr"/>
+      <c r="AW70" s="10" t="n"/>
+      <c r="AX70" s="11" t="n"/>
+      <c r="AY70" s="45" t="inlineStr"/>
+      <c r="AZ70" s="10" t="n"/>
+      <c r="BA70" s="11" t="n"/>
+      <c r="BB70" s="45" t="inlineStr"/>
+      <c r="BC70" s="10" t="n"/>
+      <c r="BD70" s="11" t="n"/>
+      <c r="BE70" s="45" t="inlineStr"/>
+      <c r="BF70" s="10" t="n"/>
+      <c r="BG70" s="11" t="n"/>
+      <c r="BH70" s="45" t="inlineStr"/>
+      <c r="BI70" s="10" t="n"/>
+      <c r="BJ70" s="11" t="n"/>
+      <c r="BK70" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL70" s="10" t="n"/>
+      <c r="BM70" s="10" t="n"/>
+      <c r="BN70" s="10" t="n"/>
+      <c r="BO70" s="10" t="n"/>
+      <c r="BP70" s="10" t="n"/>
+      <c r="BQ70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="450" customHeight="1">
+      <c r="A71" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-052</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>一覧からのプレビュー（画像 / PDF）</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`file.download` 権限あり）
+・アップロード済みファイルとして PDF 1 件・画像 1 件・Excel 1 件が存在すること
+・他JAのファイル 1 件、論理削除済みファイル 1 件も用意すること</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">アップロード済みファイル一覧で PDF のプレビュー操作を行い、GET `/api/v1/file-upload/{file_upload_id}/preview` のレスポンスを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">画像ファイルで同じ操作を行う
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DataScope 範囲外（他JA）のファイルIDを直接指定してプレビューAPIを呼び出す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">論理削除済みファイルのIDを直接指定してプレビューAPIを呼び出す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>`file.download` 権限を持たないロールでプレビューAPIを呼び出す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200が返り、`data.preview_url`（署名付きURL）と `data.file_name` が返ること。URLでファイルが表示できること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同様にプレビューできること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`NOT_FOUND`）が返ること（存在を秘匿するため403ではなく404でマスクする）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`NOT_FOUND`）が返ること（`deleted_at IS NULL` 条件で対象外）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード403（`FORBIDDEN`）が返ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・本機能は 2026/07/02 に一度本画面から削除しダウンロード画面（SCR-022）へ移行したが、顧客要件により同月中（2026/07/27）に**再追加**された。画面設計書 v1.4 / API設計書 v1.2 参照
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・プレビューは署名付きURLの発行のみで、`t_file_upload` への INSERT は行わない</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="45" t="inlineStr"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="45" t="inlineStr"/>
+      <c r="AK71" s="10" t="n"/>
+      <c r="AL71" s="11" t="n"/>
+      <c r="AM71" s="45" t="inlineStr"/>
+      <c r="AN71" s="10" t="n"/>
+      <c r="AO71" s="11" t="n"/>
+      <c r="AP71" s="45" t="inlineStr"/>
+      <c r="AQ71" s="10" t="n"/>
+      <c r="AR71" s="11" t="n"/>
+      <c r="AS71" s="45" t="inlineStr"/>
+      <c r="AT71" s="10" t="n"/>
+      <c r="AU71" s="11" t="n"/>
+      <c r="AV71" s="45" t="inlineStr"/>
+      <c r="AW71" s="10" t="n"/>
+      <c r="AX71" s="11" t="n"/>
+      <c r="AY71" s="45" t="inlineStr"/>
+      <c r="AZ71" s="10" t="n"/>
+      <c r="BA71" s="11" t="n"/>
+      <c r="BB71" s="45" t="inlineStr"/>
+      <c r="BC71" s="10" t="n"/>
+      <c r="BD71" s="11" t="n"/>
+      <c r="BE71" s="45" t="inlineStr"/>
+      <c r="BF71" s="10" t="n"/>
+      <c r="BG71" s="11" t="n"/>
+      <c r="BH71" s="45" t="inlineStr"/>
+      <c r="BI71" s="10" t="n"/>
+      <c r="BJ71" s="11" t="n"/>
+      <c r="BK71" s="46" t="inlineStr"/>
+      <c r="BL71" s="10" t="n"/>
+      <c r="BM71" s="10" t="n"/>
+      <c r="BN71" s="10" t="n"/>
+      <c r="BO71" s="10" t="n"/>
+      <c r="BP71" s="10" t="n"/>
+      <c r="BQ71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="450" customHeight="1">
+      <c r="A72" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-053</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>一覧からの単体ダウンロードと証跡</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`file.download` 権限あり）
+・アップロード済みファイルが 1 件以上存在すること</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ0（事前計測）：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB で `SELECT COUNT(*) FROM t_file_download` を実行し、テスト前の総件数を記録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">一覧でチェックボックスを1件選択してダウンロードを実行し、GET `/api/v1/file-upload/{file_upload_id}/download` のレスポンスを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ダウンロードされたファイルの内容と `Content-Type` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB で `SELECT COUNT(*) FROM t_file_download` を再実行し、ステップ0 と比較する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB で `SELECT operation, log_type FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_id DESC LIMIT 1` を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DataScope 範囲外・論理削除済みのファイルIDを直接指定してダウンロードAPIを呼び出す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200が返り、`Content-Disposition: attachment; filename="..."` でバイナリが返ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">内容が元ファイルと一致すること。`Content-Type` が拡張子から正しく判定されること（PDF → `application/pdf` 等）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_file_download` の総件数が**増加していないこと**。本画面のダウンロードは `t_file_download` へ INSERT しない（旧仕様では `download_type = 2` で履歴行を作っていたが、現行実装では作らない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`operation = 'DOWNLOAD'`・`log_type = 4`（FILE_OPERATION）の操作ログが記録されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">いずれも HTTPステータスコード404（`NOT_FOUND`）が返ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ3 は旧仕様との差分の回帰確認。アップロード時に `t_file_download` へペア行を登録する処理（#55935）とは別物であり、ダウンロード操作では行を増やさない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ストレージからの取得はトランザクション外で先に行い、取得失敗時に操作ログを残さない</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="11" t="n"/>
+      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="11" t="n"/>
+      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="11" t="n"/>
+      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="11" t="n"/>
+      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="11" t="n"/>
+      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="11" t="n"/>
+      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="11" t="n"/>
+      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="11" t="n"/>
+      <c r="BK72" s="46" t="inlineStr"/>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="450" customHeight="1">
+      <c r="A73" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-054</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>一覧からのZIP一括ダウンロード（1〜50件・重複不可）</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`file.download` 権限あり）
+・アップロード済みファイルが 51 件以上存在すること
+・DataScope 範囲外のファイル 1 件も用意すること</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">一覧で 3 件を選択してZIP一括ダウンロードを実行し、POST `/api/v1/file-upload/download-zip` のレスポンスとZIPの中身を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`file_upload_ids: []`（0件）で直接送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`file_upload_ids` に 51 件の一意なIDを指定して直接送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`file_upload_ids` に 50 件の一意なIDを指定して直接送信する（境界値・上限ちょうど）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`file_upload_ids: [id1, id1, id2]`（重複あり）で直接送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`file_upload_ids` に DataScope 範囲外のIDを1件だけ混ぜて直接送信する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_log` の記録件数を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1分間に21回 ZIP一括ダウンロードを実行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200・`Content-Type: application/zip` でZIPが返り、選択した3ファイルすべてが含まれること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`VALIDATION_ERROR`、`errors[].message` が `ファイルを選択してください。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`errors[].message` が `一括ダウンロードは最大50件までです。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード200が返ること（50件は許容範囲内）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード400（`errors[].message` が `ファイルIDが重複しています。`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`NOT_FOUND`）が返り、ZIPが生成されないこと。**部分成功はしない**（1件でも範囲外なら全体を拒否する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ZIP全体で操作ログが**1件のみ**記録されること（ファイルごとには記録しない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">21回目が HTTPステータスコード429（`TOO_MANY_REQUESTS`）となること（レート制限 20回/分）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・整数以外を指定した場合は `ファイルIDは整数で指定してください。`、配列でない場合は `ファイルIDの形式が不正です。`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ステップ6の「部分成功しない」は、ZIPを開くまで欠落に気付けないため全体拒否とする設計</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="45" t="inlineStr"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="45" t="inlineStr"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="45" t="inlineStr"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="11" t="n"/>
+      <c r="AP73" s="45" t="inlineStr"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="11" t="n"/>
+      <c r="AS73" s="45" t="inlineStr"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="11" t="n"/>
+      <c r="AV73" s="45" t="inlineStr"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="11" t="n"/>
+      <c r="AY73" s="45" t="inlineStr"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="11" t="n"/>
+      <c r="BB73" s="45" t="inlineStr"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="11" t="n"/>
+      <c r="BE73" s="45" t="inlineStr"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="11" t="n"/>
+      <c r="BH73" s="45" t="inlineStr"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="11" t="n"/>
+      <c r="BK73" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="940">
+  <mergeCells count="992">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
-    <mergeCell ref="BB68:BD68"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -16229,6 +17355,7 @@
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
+    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
@@ -16236,19 +17363,21 @@
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
-    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="AP73:AR73"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
@@ -16257,6 +17386,7 @@
     <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
@@ -16269,7 +17399,6 @@
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
-    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
@@ -16294,7 +17423,7 @@
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
-    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
@@ -16311,6 +17440,7 @@
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
@@ -16355,6 +17485,7 @@
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="BE29:BG29"/>
@@ -16365,8 +17496,8 @@
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
-    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="AS72:AU72"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -16385,10 +17516,11 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="AJ69:AL69"/>
     <mergeCell ref="BK69:BQ69"/>
+    <mergeCell ref="AM70:AO70"/>
+    <mergeCell ref="AE71:AF71"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
-    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="AG66:AI66"/>
@@ -16401,16 +17533,16 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
-    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AP72:AR72"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
-    <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="AS20:AU20"/>
@@ -16418,9 +17550,11 @@
     <mergeCell ref="BK18:BQ18"/>
     <mergeCell ref="A19:BQ19"/>
     <mergeCell ref="AY22:BA22"/>
+    <mergeCell ref="A68:BQ68"/>
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
@@ -16457,6 +17591,7 @@
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="AE73:AF73"/>
     <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
@@ -16467,14 +17602,15 @@
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="BK72:BQ72"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
-    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
@@ -16489,12 +17625,13 @@
     <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="Q65:W65"/>
-    <mergeCell ref="AY68:BA68"/>
+    <mergeCell ref="BH71:BJ71"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="BH73:BJ73"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
@@ -16504,6 +17641,7 @@
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
+    <mergeCell ref="BE70:BG70"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -16520,6 +17658,7 @@
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
@@ -16533,6 +17672,7 @@
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="AG65:AI65"/>
+    <mergeCell ref="X73:AD73"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
@@ -16541,7 +17681,6 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
-    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
@@ -16556,10 +17695,12 @@
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="BH67:BJ67"/>
+    <mergeCell ref="BE71:BG71"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
+    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
@@ -16569,6 +17710,7 @@
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="AY69:BA69"/>
+    <mergeCell ref="Q71:W71"/>
     <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="X61:AD61"/>
@@ -16579,6 +17721,7 @@
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="AV26:AX26"/>
+    <mergeCell ref="Q73:W73"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
@@ -16588,9 +17731,12 @@
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="J70:P70"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AM71:AO71"/>
     <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
@@ -16605,11 +17751,13 @@
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="E71:I71"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
@@ -16634,23 +17782,27 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="BB71:BD71"/>
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
+    <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AY72:BA72"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="BB73:BD73"/>
     <mergeCell ref="Q49:W49"/>
-    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="AV73:AX73"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="AV48:AX48"/>
@@ -16668,15 +17820,21 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
+    <mergeCell ref="AS70:AU70"/>
+    <mergeCell ref="J71:P71"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="AM73:AO73"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
     <mergeCell ref="BK30:BQ30"/>
     <mergeCell ref="BK36:BQ36"/>
     <mergeCell ref="AS47:AU47"/>
+    <mergeCell ref="J73:P73"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
@@ -16693,6 +17851,7 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="AV66:AX66"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -16707,6 +17866,7 @@
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="AP64:AR64"/>
@@ -16764,6 +17924,8 @@
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH69:BJ69"/>
+    <mergeCell ref="AS73:AU73"/>
+    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
@@ -16790,6 +17952,7 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
@@ -16812,7 +17975,6 @@
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
-    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="J69:P69"/>
@@ -16826,6 +17988,7 @@
     <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
@@ -16867,6 +18030,7 @@
     <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
@@ -16881,7 +18045,9 @@
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="AJ71:AL71"/>
     <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="BK71:BQ71"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="AJ58:AL58"/>
@@ -16891,7 +18057,9 @@
     <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AJ73:AL73"/>
     <mergeCell ref="AP35:AR35"/>
+    <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
@@ -16900,6 +18068,8 @@
     <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
@@ -16907,7 +18077,6 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
-    <mergeCell ref="AJ68:AL68"/>
     <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
@@ -16917,11 +18086,12 @@
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="BE73:BG73"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
@@ -17000,6 +18170,7 @@
     <mergeCell ref="E61:I61"/>
     <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="AG73:AI73"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -17030,7 +18201,6 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="A60:BQ60"/>
     <mergeCell ref="AP31:AR31"/>
@@ -17049,6 +18219,7 @@
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J72:P72"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
@@ -17089,19 +18260,26 @@
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
+    <mergeCell ref="BE72:BG72"/>
+    <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AV72:AX72"/>
     <mergeCell ref="E64:I64"/>
+    <mergeCell ref="AY73:BA73"/>
+    <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
+    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
@@ -17121,6 +18299,7 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="B71:D71"/>
     <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="AM28:AO28"/>
@@ -17133,13 +18312,13 @@
     <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE31 AE33:AE44 AE46:AE54 AE56:AE59 AE61:AE69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE31 AE33:AE44 AE46:AE54 AE56:AE59 AE61:AE67 AE69:AE73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG31 AG33:AG44 AG46:AG54 AG56:AG59 AG61:AG69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG31 AG33:AG44 AG46:AG54 AG56:AG59 AG61:AG67 AG69:AG73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV31 AV33:AV44 AV46:AV54 AV56:AV59 AV61:AV69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV31 AV33:AV44 AV46:AV54 AV56:AV59 AV61:AV67 AV69:AV73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
